--- a/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
+++ b/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="184">
   <si>
     <t>meta_y_factor</t>
   </si>
@@ -133,171 +133,180 @@
     <t>acm</t>
   </si>
   <si>
+    <t>mig_rate</t>
+  </si>
+  <si>
+    <t>hepb_prev</t>
+  </si>
+  <si>
+    <t>diagnosed_meas</t>
+  </si>
+  <si>
+    <t>linked_meas</t>
+  </si>
+  <si>
+    <t>treat_cov</t>
+  </si>
+  <si>
+    <t>epos_total</t>
+  </si>
+  <si>
+    <t>hep_dth</t>
+  </si>
+  <si>
+    <t>imig_vax_prop</t>
+  </si>
+  <si>
+    <t>imig_clr_prop</t>
+  </si>
+  <si>
+    <t>tx_chb_cc</t>
+  </si>
+  <si>
+    <t>tx_chb_hcc</t>
+  </si>
+  <si>
+    <t>tx_cir_hcc</t>
+  </si>
+  <si>
+    <t>tx_cc_dc</t>
+  </si>
+  <si>
+    <t>dc_cc_t</t>
+  </si>
+  <si>
+    <t>tx_dc_death</t>
+  </si>
+  <si>
+    <t>sh_si_t</t>
+  </si>
+  <si>
+    <t>eh_si</t>
+  </si>
+  <si>
+    <t>acu_chb</t>
+  </si>
+  <si>
+    <t>acu_dth</t>
+  </si>
+  <si>
+    <t>ei_eh</t>
+  </si>
+  <si>
+    <t>si_sh</t>
+  </si>
+  <si>
+    <t>sh_si</t>
+  </si>
+  <si>
+    <t>eh_cc_in</t>
+  </si>
+  <si>
+    <t>sh_cc_in</t>
+  </si>
+  <si>
+    <t>cc_dc</t>
+  </si>
+  <si>
+    <t>ei_hcc_in</t>
+  </si>
+  <si>
+    <t>act_hcc_in</t>
+  </si>
+  <si>
+    <t>si_hcc_in</t>
+  </si>
+  <si>
+    <t>cir_hcc_in</t>
+  </si>
+  <si>
+    <t>dc_dth</t>
+  </si>
+  <si>
+    <t>hcc_dth</t>
+  </si>
+  <si>
+    <t>chb_clr</t>
+  </si>
+  <si>
+    <t>y_hcc</t>
+  </si>
+  <si>
+    <t>y_cc</t>
+  </si>
+  <si>
+    <t>foi_cal</t>
+  </si>
+  <si>
+    <t>anc_scr</t>
+  </si>
+  <si>
+    <t>pregs</t>
+  </si>
+  <si>
+    <t>nullipar</t>
+  </si>
+  <si>
+    <t>preg_ltc_rate</t>
+  </si>
+  <si>
+    <t>ve_hepbd_lvl</t>
+  </si>
+  <si>
+    <t>ve_hepbd_hvl</t>
+  </si>
+  <si>
+    <t>ve_hepbd_pap</t>
+  </si>
+  <si>
+    <t>ve_hepb3</t>
+  </si>
+  <si>
+    <t>mtct_chb</t>
+  </si>
+  <si>
+    <t>trisk_low</t>
+  </si>
+  <si>
+    <t>trisk_high</t>
+  </si>
+  <si>
+    <t>hepbd_cov</t>
+  </si>
+  <si>
+    <t>hepb3_cov</t>
+  </si>
+  <si>
+    <t>hvl_epos</t>
+  </si>
+  <si>
+    <t>hvl_eneg</t>
+  </si>
+  <si>
+    <t>ts_rate</t>
+  </si>
+  <si>
+    <t>ltf_rate</t>
+  </si>
+  <si>
+    <t>diag_measure</t>
+  </si>
+  <si>
+    <t>ltc_measure</t>
+  </si>
+  <si>
+    <t>treat_measure</t>
+  </si>
+  <si>
+    <t>imig_rate</t>
+  </si>
+  <si>
     <t>emig_rate</t>
   </si>
   <si>
-    <t>hepb_prev</t>
-  </si>
-  <si>
-    <t>diagnosed_meas</t>
-  </si>
-  <si>
-    <t>linked_meas</t>
-  </si>
-  <si>
-    <t>treat_cov</t>
-  </si>
-  <si>
-    <t>epos_total</t>
-  </si>
-  <si>
-    <t>imig_rate</t>
-  </si>
-  <si>
     <t>imig_prev</t>
   </si>
   <si>
-    <t>imig_vax_prop</t>
-  </si>
-  <si>
-    <t>imig_clr_prop</t>
-  </si>
-  <si>
-    <t>tx_chb_cc</t>
-  </si>
-  <si>
-    <t>tx_chb_hcc</t>
-  </si>
-  <si>
-    <t>tx_cir_hcc</t>
-  </si>
-  <si>
-    <t>tx_cc_dc</t>
-  </si>
-  <si>
-    <t>dc_cc_t</t>
-  </si>
-  <si>
-    <t>tx_dc_death</t>
-  </si>
-  <si>
-    <t>sh_si_t</t>
-  </si>
-  <si>
-    <t>eh_si</t>
-  </si>
-  <si>
-    <t>acu_chb</t>
-  </si>
-  <si>
-    <t>acu_dth</t>
-  </si>
-  <si>
-    <t>ei_eh</t>
-  </si>
-  <si>
-    <t>si_sh</t>
-  </si>
-  <si>
-    <t>sh_si</t>
-  </si>
-  <si>
-    <t>eh_cc_in</t>
-  </si>
-  <si>
-    <t>sh_cc_in</t>
-  </si>
-  <si>
-    <t>cc_dc</t>
-  </si>
-  <si>
-    <t>ei_hcc_in</t>
-  </si>
-  <si>
-    <t>act_hcc_in</t>
-  </si>
-  <si>
-    <t>si_hcc_in</t>
-  </si>
-  <si>
-    <t>cir_hcc_in</t>
-  </si>
-  <si>
-    <t>dc_dth</t>
-  </si>
-  <si>
-    <t>hcc_dth</t>
-  </si>
-  <si>
-    <t>y_hcc</t>
-  </si>
-  <si>
-    <t>y_cc</t>
-  </si>
-  <si>
-    <t>foi_cal</t>
-  </si>
-  <si>
-    <t>anc_scr</t>
-  </si>
-  <si>
-    <t>pregs</t>
-  </si>
-  <si>
-    <t>nullipar</t>
-  </si>
-  <si>
-    <t>preg_ltc_rate</t>
-  </si>
-  <si>
-    <t>ve_hepbd_lvl</t>
-  </si>
-  <si>
-    <t>ve_hepbd_hvl</t>
-  </si>
-  <si>
-    <t>ve_hepbd_pap</t>
-  </si>
-  <si>
-    <t>ve_hepb3</t>
-  </si>
-  <si>
-    <t>mtct_chb</t>
-  </si>
-  <si>
-    <t>trisk_low</t>
-  </si>
-  <si>
-    <t>trisk_high</t>
-  </si>
-  <si>
-    <t>hepbd_cov</t>
-  </si>
-  <si>
-    <t>hepb3_cov</t>
-  </si>
-  <si>
-    <t>hvl_epos</t>
-  </si>
-  <si>
-    <t>hvl_eneg</t>
-  </si>
-  <si>
-    <t>ts_rate</t>
-  </si>
-  <si>
-    <t>ltf_rate</t>
-  </si>
-  <si>
-    <t>diag_measure</t>
-  </si>
-  <si>
-    <t>ltc_measure</t>
-  </si>
-  <si>
-    <t>treat_measure</t>
-  </si>
-  <si>
     <t>imig_rem</t>
   </si>
   <si>
@@ -545,6 +554,9 @@
   </si>
   <si>
     <t>treat_rate</t>
+  </si>
+  <si>
+    <t>inc_hcc</t>
   </si>
   <si>
     <t>mx_mtct</t>
@@ -911,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA195"/>
+  <dimension ref="A1:AA200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
@@ -1897,76 +1909,76 @@
         <v>1</v>
       </c>
       <c r="D13">
+        <v>0.1874999999999999</v>
+      </c>
+      <c r="E13">
         <v>0.9</v>
       </c>
-      <c r="E13">
-        <v>0.975</v>
-      </c>
       <c r="F13">
-        <v>3.053125</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>0.1874999999999999</v>
+        <v>0.1775390625</v>
       </c>
       <c r="H13">
-        <v>0.1</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="I13">
-        <v>3.1671142578125</v>
+        <v>1</v>
       </c>
       <c r="J13">
+        <v>0.6937500000000001</v>
+      </c>
+      <c r="K13">
+        <v>0.1242187499999999</v>
+      </c>
+      <c r="L13">
+        <v>1.1125</v>
+      </c>
+      <c r="M13">
+        <v>2.85722770690918</v>
+      </c>
+      <c r="N13">
+        <v>0.5249999999999999</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>0.8</v>
+      </c>
+      <c r="Q13">
         <v>0.9</v>
       </c>
-      <c r="K13">
-        <v>0.1</v>
-      </c>
-      <c r="L13">
-        <v>1.0125</v>
-      </c>
-      <c r="M13">
-        <v>0.1</v>
-      </c>
-      <c r="N13">
-        <v>0.1</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13">
-        <v>0.1</v>
-      </c>
-      <c r="Q13">
-        <v>0.1</v>
-      </c>
       <c r="R13">
-        <v>1.7125</v>
+        <v>1</v>
       </c>
       <c r="S13">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="T13">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="U13">
-        <v>1.475</v>
+        <v>1</v>
       </c>
       <c r="V13">
         <v>0.1</v>
       </c>
       <c r="W13">
+        <v>0.575</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
         <v>0.1</v>
       </c>
-      <c r="X13">
-        <v>0.75</v>
-      </c>
-      <c r="Y13">
-        <v>0.75</v>
-      </c>
       <c r="Z13">
-        <v>0.1</v>
+        <v>0.2374999999999999</v>
       </c>
       <c r="AA13">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -1978,76 +1990,76 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
-        <v>1.8125</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>1.475</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>4.193884277343749</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="M14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="N14">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O14">
-        <v>0.60625</v>
+        <v>1</v>
       </c>
       <c r="P14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="R14">
-        <v>2.57724609375</v>
+        <v>1</v>
       </c>
       <c r="S14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="T14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>4.535011291503906</v>
+        <v>1</v>
       </c>
       <c r="V14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="W14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="X14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z14">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="AA14">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -3274,76 +3286,76 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="L30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="M30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="O30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="P30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="R30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="S30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="T30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="U30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="V30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="W30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="Y30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="Z30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="AA30">
-        <v>1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -4732,76 +4744,76 @@
         <v>1</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0.07784846305847154</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2.347647125990987</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>0.03569866733551025</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0.94388671875</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J48">
-        <v>1</v>
+        <v>1.49325927734375</v>
       </c>
       <c r="K48">
-        <v>1</v>
+        <v>6.784080180466175</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>1.797608623504639</v>
       </c>
       <c r="M48">
-        <v>1</v>
+        <v>0.8387500000000001</v>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>4.190825419127941</v>
       </c>
       <c r="O48">
-        <v>1</v>
+        <v>1.804707641601563</v>
       </c>
       <c r="P48">
-        <v>1</v>
+        <v>1.191767578125</v>
       </c>
       <c r="Q48">
-        <v>1</v>
+        <v>7.376191635131836</v>
       </c>
       <c r="R48">
-        <v>1</v>
+        <v>1.568143908441438</v>
       </c>
       <c r="S48">
-        <v>1</v>
+        <v>0.76796875</v>
       </c>
       <c r="T48">
-        <v>1</v>
+        <v>4.475347220897674</v>
       </c>
       <c r="U48">
-        <v>1</v>
+        <v>1.725154495239258</v>
       </c>
       <c r="V48">
-        <v>1</v>
+        <v>1.6812744140625</v>
       </c>
       <c r="W48">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y48">
-        <v>1</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="Z48">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AA48">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -6532,28 +6544,28 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K70">
         <v>1</v>
       </c>
       <c r="L70">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="M70">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N70">
         <v>1</v>
       </c>
       <c r="O70">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P70">
         <v>1</v>
       </c>
       <c r="Q70">
-        <v>1</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="R70">
         <v>1</v>
@@ -6562,7 +6574,7 @@
         <v>1</v>
       </c>
       <c r="T70">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U70">
         <v>1</v>
@@ -6571,16 +6583,16 @@
         <v>1</v>
       </c>
       <c r="W70">
-        <v>1</v>
+        <v>0.825</v>
       </c>
       <c r="X70">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y70">
         <v>1</v>
       </c>
       <c r="Z70">
-        <v>1</v>
+        <v>1.15625</v>
       </c>
       <c r="AA70">
         <v>1</v>
@@ -13151,73 +13163,329 @@
       <c r="A152" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="B152" s="1"/>
       <c r="C152">
         <v>1</v>
       </c>
       <c r="D152">
         <v>1</v>
       </c>
+      <c r="E152">
+        <v>1</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
       <c r="G152">
+        <v>1</v>
+      </c>
+      <c r="H152">
+        <v>1</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+      <c r="J152">
+        <v>1</v>
+      </c>
+      <c r="K152">
+        <v>1</v>
+      </c>
+      <c r="L152">
+        <v>1</v>
+      </c>
+      <c r="M152">
+        <v>1</v>
+      </c>
+      <c r="N152">
+        <v>1</v>
+      </c>
+      <c r="O152">
+        <v>1</v>
+      </c>
+      <c r="P152">
+        <v>1</v>
+      </c>
+      <c r="Q152">
+        <v>1</v>
+      </c>
+      <c r="R152">
+        <v>1</v>
+      </c>
+      <c r="S152">
+        <v>1</v>
+      </c>
+      <c r="T152">
+        <v>1</v>
+      </c>
+      <c r="U152">
+        <v>1</v>
+      </c>
+      <c r="V152">
+        <v>1</v>
+      </c>
+      <c r="W152">
+        <v>1</v>
+      </c>
+      <c r="X152">
+        <v>1</v>
+      </c>
+      <c r="Y152">
+        <v>1</v>
+      </c>
+      <c r="Z152">
+        <v>1</v>
+      </c>
+      <c r="AA152">
         <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:27">
       <c r="A153" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="B153" s="1"/>
       <c r="C153">
         <v>1</v>
       </c>
+      <c r="D153">
+        <v>1</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <v>1</v>
+      </c>
+      <c r="H153">
+        <v>1</v>
+      </c>
+      <c r="I153">
+        <v>1</v>
+      </c>
       <c r="J153">
         <v>1</v>
       </c>
+      <c r="K153">
+        <v>1</v>
+      </c>
+      <c r="L153">
+        <v>1</v>
+      </c>
       <c r="M153">
+        <v>1</v>
+      </c>
+      <c r="N153">
+        <v>1</v>
+      </c>
+      <c r="O153">
+        <v>1</v>
+      </c>
+      <c r="P153">
+        <v>1</v>
+      </c>
+      <c r="Q153">
+        <v>1</v>
+      </c>
+      <c r="R153">
+        <v>1</v>
+      </c>
+      <c r="S153">
+        <v>1</v>
+      </c>
+      <c r="T153">
+        <v>1</v>
+      </c>
+      <c r="U153">
+        <v>1</v>
+      </c>
+      <c r="V153">
+        <v>1</v>
+      </c>
+      <c r="W153">
+        <v>1</v>
+      </c>
+      <c r="X153">
+        <v>1</v>
+      </c>
+      <c r="Y153">
+        <v>1</v>
+      </c>
+      <c r="Z153">
+        <v>1</v>
+      </c>
+      <c r="AA153">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:27">
       <c r="A154" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="B154" s="1"/>
       <c r="C154">
         <v>1</v>
       </c>
+      <c r="D154">
+        <v>1</v>
+      </c>
+      <c r="E154">
+        <v>1</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+      <c r="H154">
+        <v>1</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>1</v>
+      </c>
+      <c r="L154">
+        <v>1</v>
+      </c>
+      <c r="M154">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>1</v>
+      </c>
+      <c r="O154">
+        <v>1</v>
+      </c>
       <c r="P154">
         <v>1</v>
       </c>
+      <c r="Q154">
+        <v>1</v>
+      </c>
+      <c r="R154">
+        <v>1</v>
+      </c>
       <c r="S154">
+        <v>1</v>
+      </c>
+      <c r="T154">
+        <v>1</v>
+      </c>
+      <c r="U154">
+        <v>1</v>
+      </c>
+      <c r="V154">
+        <v>1</v>
+      </c>
+      <c r="W154">
+        <v>1</v>
+      </c>
+      <c r="X154">
+        <v>1</v>
+      </c>
+      <c r="Y154">
+        <v>1</v>
+      </c>
+      <c r="Z154">
+        <v>1</v>
+      </c>
+      <c r="AA154">
         <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:27">
       <c r="A155" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="B155" s="1"/>
       <c r="C155">
         <v>1</v>
       </c>
+      <c r="D155">
+        <v>1</v>
+      </c>
+      <c r="E155">
+        <v>1</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="H155">
+        <v>1</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="J155">
+        <v>1</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155">
+        <v>1</v>
+      </c>
+      <c r="M155">
+        <v>1</v>
+      </c>
+      <c r="N155">
+        <v>1</v>
+      </c>
+      <c r="O155">
+        <v>1</v>
+      </c>
+      <c r="P155">
+        <v>1</v>
+      </c>
+      <c r="Q155">
+        <v>1</v>
+      </c>
+      <c r="R155">
+        <v>1</v>
+      </c>
+      <c r="S155">
+        <v>1</v>
+      </c>
+      <c r="T155">
+        <v>1</v>
+      </c>
+      <c r="U155">
+        <v>1</v>
+      </c>
       <c r="V155">
         <v>1</v>
       </c>
+      <c r="W155">
+        <v>1</v>
+      </c>
+      <c r="X155">
+        <v>1</v>
+      </c>
       <c r="Y155">
+        <v>1</v>
+      </c>
+      <c r="Z155">
+        <v>1</v>
+      </c>
+      <c r="AA155">
         <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:27">
       <c r="A156" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>1</v>
@@ -13226,30 +13494,15 @@
         <v>1</v>
       </c>
       <c r="D156">
-        <v>1</v>
-      </c>
-      <c r="E156">
-        <v>1</v>
-      </c>
-      <c r="F156">
-        <v>1</v>
-      </c>
-      <c r="G156">
-        <v>1</v>
-      </c>
-      <c r="H156">
-        <v>1</v>
-      </c>
-      <c r="I156">
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:27">
       <c r="A157" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -13257,637 +13510,589 @@
       <c r="D157">
         <v>1</v>
       </c>
-      <c r="E157">
-        <v>1</v>
-      </c>
-      <c r="F157">
-        <v>1</v>
-      </c>
       <c r="G157">
-        <v>1</v>
-      </c>
-      <c r="H157">
-        <v>1</v>
-      </c>
-      <c r="I157">
         <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:27">
       <c r="A158" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C158">
         <v>1</v>
       </c>
-      <c r="D158">
-        <v>1</v>
-      </c>
-      <c r="E158">
-        <v>1</v>
-      </c>
-      <c r="F158">
-        <v>1</v>
-      </c>
-      <c r="G158">
-        <v>1</v>
-      </c>
-      <c r="H158">
-        <v>1</v>
-      </c>
-      <c r="I158">
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="M158">
         <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:27">
       <c r="A159" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C159">
         <v>1</v>
       </c>
-      <c r="D159">
-        <v>1</v>
-      </c>
-      <c r="E159">
-        <v>1</v>
-      </c>
-      <c r="F159">
-        <v>1</v>
-      </c>
-      <c r="G159">
-        <v>1</v>
-      </c>
-      <c r="H159">
-        <v>1</v>
-      </c>
-      <c r="I159">
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="M159">
         <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:27">
       <c r="A160" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B160" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="J160">
+        <v>1</v>
+      </c>
+      <c r="M160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21">
+      <c r="A161" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+      <c r="D161">
+        <v>1</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161">
+        <v>1</v>
+      </c>
+      <c r="H161">
+        <v>1</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21">
+      <c r="A162" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="D162">
+        <v>1</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+      <c r="H162">
+        <v>1</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21">
+      <c r="A163" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="D163">
+        <v>1</v>
+      </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+      <c r="H163">
+        <v>1</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21">
+      <c r="A164" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164">
+        <v>1</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="G164">
+        <v>1</v>
+      </c>
+      <c r="H164">
+        <v>1</v>
+      </c>
+      <c r="I164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21">
+      <c r="A165" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C160">
-        <v>1</v>
-      </c>
-      <c r="D160">
-        <v>1</v>
-      </c>
-      <c r="E160">
-        <v>1</v>
-      </c>
-      <c r="F160">
-        <v>1</v>
-      </c>
-      <c r="G160">
-        <v>1</v>
-      </c>
-      <c r="H160">
-        <v>1</v>
-      </c>
-      <c r="I160">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:27">
-      <c r="A161" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B161" s="1" t="s">
+      <c r="C165">
+        <v>1</v>
+      </c>
+      <c r="D165">
+        <v>1</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="G165">
+        <v>1</v>
+      </c>
+      <c r="H165">
+        <v>1</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21">
+      <c r="A166" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C161">
-        <v>1</v>
-      </c>
-      <c r="D161">
-        <v>1</v>
-      </c>
-      <c r="E161">
-        <v>1</v>
-      </c>
-      <c r="F161">
-        <v>1</v>
-      </c>
-      <c r="G161">
-        <v>1</v>
-      </c>
-      <c r="H161">
-        <v>1</v>
-      </c>
-      <c r="I161">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:27">
-      <c r="A162" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B162" s="1" t="s">
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="D166">
+        <v>1</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
+      <c r="F166">
+        <v>1</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+      <c r="H166">
+        <v>1</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:21">
+      <c r="A167" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C162">
-        <v>1</v>
-      </c>
-      <c r="J162">
-        <v>1</v>
-      </c>
-      <c r="K162">
-        <v>1</v>
-      </c>
-      <c r="L162">
-        <v>1</v>
-      </c>
-      <c r="M162">
-        <v>1</v>
-      </c>
-      <c r="N162">
-        <v>1</v>
-      </c>
-      <c r="O162">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:27">
-      <c r="A163" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B163" s="1" t="s">
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167">
+        <v>1</v>
+      </c>
+      <c r="M167">
+        <v>1</v>
+      </c>
+      <c r="N167">
+        <v>1</v>
+      </c>
+      <c r="O167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21">
+      <c r="A168" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C163">
-        <v>1</v>
-      </c>
-      <c r="J163">
-        <v>1</v>
-      </c>
-      <c r="K163">
-        <v>1</v>
-      </c>
-      <c r="L163">
-        <v>1</v>
-      </c>
-      <c r="M163">
-        <v>1</v>
-      </c>
-      <c r="N163">
-        <v>1</v>
-      </c>
-      <c r="O163">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:27">
-      <c r="A164" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B164" s="1" t="s">
+      <c r="C168">
+        <v>1</v>
+      </c>
+      <c r="J168">
+        <v>1</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168">
+        <v>1</v>
+      </c>
+      <c r="M168">
+        <v>1</v>
+      </c>
+      <c r="N168">
+        <v>1</v>
+      </c>
+      <c r="O168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21">
+      <c r="A169" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C164">
-        <v>1</v>
-      </c>
-      <c r="J164">
-        <v>1</v>
-      </c>
-      <c r="K164">
-        <v>1</v>
-      </c>
-      <c r="L164">
-        <v>1</v>
-      </c>
-      <c r="M164">
-        <v>1</v>
-      </c>
-      <c r="N164">
-        <v>1</v>
-      </c>
-      <c r="O164">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:27">
-      <c r="A165" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B165" s="1" t="s">
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="J169">
+        <v>1</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169">
+        <v>1</v>
+      </c>
+      <c r="M169">
+        <v>1</v>
+      </c>
+      <c r="N169">
+        <v>1</v>
+      </c>
+      <c r="O169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21">
+      <c r="A170" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C165">
-        <v>1</v>
-      </c>
-      <c r="J165">
-        <v>1</v>
-      </c>
-      <c r="K165">
-        <v>1</v>
-      </c>
-      <c r="L165">
-        <v>1</v>
-      </c>
-      <c r="M165">
-        <v>1</v>
-      </c>
-      <c r="N165">
-        <v>1</v>
-      </c>
-      <c r="O165">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:27">
-      <c r="A166" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B166" s="1" t="s">
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>1</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+      <c r="N170">
+        <v>1</v>
+      </c>
+      <c r="O170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21">
+      <c r="A171" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C166">
-        <v>1</v>
-      </c>
-      <c r="J166">
-        <v>1</v>
-      </c>
-      <c r="K166">
-        <v>1</v>
-      </c>
-      <c r="L166">
-        <v>1</v>
-      </c>
-      <c r="M166">
-        <v>1</v>
-      </c>
-      <c r="N166">
-        <v>1</v>
-      </c>
-      <c r="O166">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:27">
-      <c r="A167" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B167" s="1" t="s">
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>1</v>
+      </c>
+      <c r="O171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:21">
+      <c r="A172" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C167">
-        <v>1</v>
-      </c>
-      <c r="J167">
-        <v>1</v>
-      </c>
-      <c r="K167">
-        <v>1</v>
-      </c>
-      <c r="L167">
-        <v>1</v>
-      </c>
-      <c r="M167">
-        <v>1</v>
-      </c>
-      <c r="N167">
-        <v>1</v>
-      </c>
-      <c r="O167">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:27">
-      <c r="A168" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B168" s="1" t="s">
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>1</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>1</v>
+      </c>
+      <c r="M172">
+        <v>1</v>
+      </c>
+      <c r="N172">
+        <v>1</v>
+      </c>
+      <c r="O172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21">
+      <c r="A173" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C168">
-        <v>1</v>
-      </c>
-      <c r="P168">
-        <v>1</v>
-      </c>
-      <c r="Q168">
-        <v>1</v>
-      </c>
-      <c r="R168">
-        <v>1</v>
-      </c>
-      <c r="S168">
-        <v>1</v>
-      </c>
-      <c r="T168">
-        <v>1</v>
-      </c>
-      <c r="U168">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:27">
-      <c r="A169" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B169" s="1" t="s">
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="P173">
+        <v>1</v>
+      </c>
+      <c r="Q173">
+        <v>1</v>
+      </c>
+      <c r="R173">
+        <v>1</v>
+      </c>
+      <c r="S173">
+        <v>1</v>
+      </c>
+      <c r="T173">
+        <v>1</v>
+      </c>
+      <c r="U173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21">
+      <c r="A174" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C169">
-        <v>1</v>
-      </c>
-      <c r="P169">
-        <v>1</v>
-      </c>
-      <c r="Q169">
-        <v>1</v>
-      </c>
-      <c r="R169">
-        <v>1</v>
-      </c>
-      <c r="S169">
-        <v>1</v>
-      </c>
-      <c r="T169">
-        <v>1</v>
-      </c>
-      <c r="U169">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:27">
-      <c r="A170" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B170" s="1" t="s">
+      <c r="C174">
+        <v>1</v>
+      </c>
+      <c r="P174">
+        <v>1</v>
+      </c>
+      <c r="Q174">
+        <v>1</v>
+      </c>
+      <c r="R174">
+        <v>1</v>
+      </c>
+      <c r="S174">
+        <v>1</v>
+      </c>
+      <c r="T174">
+        <v>1</v>
+      </c>
+      <c r="U174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21">
+      <c r="A175" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C170">
-        <v>1</v>
-      </c>
-      <c r="P170">
-        <v>1</v>
-      </c>
-      <c r="Q170">
-        <v>1</v>
-      </c>
-      <c r="R170">
-        <v>1</v>
-      </c>
-      <c r="S170">
-        <v>1</v>
-      </c>
-      <c r="T170">
-        <v>1</v>
-      </c>
-      <c r="U170">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:27">
-      <c r="A171" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B171" s="1" t="s">
+      <c r="C175">
+        <v>1</v>
+      </c>
+      <c r="P175">
+        <v>1</v>
+      </c>
+      <c r="Q175">
+        <v>1</v>
+      </c>
+      <c r="R175">
+        <v>1</v>
+      </c>
+      <c r="S175">
+        <v>1</v>
+      </c>
+      <c r="T175">
+        <v>1</v>
+      </c>
+      <c r="U175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:21">
+      <c r="A176" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C171">
-        <v>1</v>
-      </c>
-      <c r="P171">
-        <v>1</v>
-      </c>
-      <c r="Q171">
-        <v>1</v>
-      </c>
-      <c r="R171">
-        <v>1</v>
-      </c>
-      <c r="S171">
-        <v>1</v>
-      </c>
-      <c r="T171">
-        <v>1</v>
-      </c>
-      <c r="U171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:27">
-      <c r="A172" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C172">
-        <v>1</v>
-      </c>
-      <c r="P172">
-        <v>1</v>
-      </c>
-      <c r="Q172">
-        <v>1</v>
-      </c>
-      <c r="R172">
-        <v>1</v>
-      </c>
-      <c r="S172">
-        <v>1</v>
-      </c>
-      <c r="T172">
-        <v>1</v>
-      </c>
-      <c r="U172">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:27">
-      <c r="A173" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C173">
-        <v>1</v>
-      </c>
-      <c r="P173">
-        <v>1</v>
-      </c>
-      <c r="Q173">
-        <v>1</v>
-      </c>
-      <c r="R173">
-        <v>1</v>
-      </c>
-      <c r="S173">
-        <v>1</v>
-      </c>
-      <c r="T173">
-        <v>1</v>
-      </c>
-      <c r="U173">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:27">
-      <c r="A174" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C174">
-        <v>1</v>
-      </c>
-      <c r="V174">
-        <v>1</v>
-      </c>
-      <c r="W174">
-        <v>1</v>
-      </c>
-      <c r="X174">
-        <v>1</v>
-      </c>
-      <c r="Y174">
-        <v>1</v>
-      </c>
-      <c r="Z174">
-        <v>1</v>
-      </c>
-      <c r="AA174">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:27">
-      <c r="A175" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C175">
-        <v>1</v>
-      </c>
-      <c r="V175">
-        <v>1</v>
-      </c>
-      <c r="W175">
-        <v>1</v>
-      </c>
-      <c r="X175">
-        <v>1</v>
-      </c>
-      <c r="Y175">
-        <v>1</v>
-      </c>
-      <c r="Z175">
-        <v>1</v>
-      </c>
-      <c r="AA175">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:27">
-      <c r="A176" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C176">
         <v>1</v>
       </c>
-      <c r="V176">
-        <v>1</v>
-      </c>
-      <c r="W176">
-        <v>1</v>
-      </c>
-      <c r="X176">
-        <v>1</v>
-      </c>
-      <c r="Y176">
-        <v>1</v>
-      </c>
-      <c r="Z176">
-        <v>1</v>
-      </c>
-      <c r="AA176">
+      <c r="P176">
+        <v>1</v>
+      </c>
+      <c r="Q176">
+        <v>1</v>
+      </c>
+      <c r="R176">
+        <v>1</v>
+      </c>
+      <c r="S176">
+        <v>1</v>
+      </c>
+      <c r="T176">
+        <v>1</v>
+      </c>
+      <c r="U176">
         <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:27">
       <c r="A177" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C177">
         <v>1</v>
       </c>
-      <c r="V177">
-        <v>1</v>
-      </c>
-      <c r="W177">
-        <v>1</v>
-      </c>
-      <c r="X177">
-        <v>1</v>
-      </c>
-      <c r="Y177">
-        <v>1</v>
-      </c>
-      <c r="Z177">
-        <v>1</v>
-      </c>
-      <c r="AA177">
+      <c r="P177">
+        <v>1</v>
+      </c>
+      <c r="Q177">
+        <v>1</v>
+      </c>
+      <c r="R177">
+        <v>1</v>
+      </c>
+      <c r="S177">
+        <v>1</v>
+      </c>
+      <c r="T177">
+        <v>1</v>
+      </c>
+      <c r="U177">
         <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:27">
       <c r="A178" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C178">
         <v>1</v>
       </c>
-      <c r="V178">
-        <v>1</v>
-      </c>
-      <c r="W178">
-        <v>1</v>
-      </c>
-      <c r="X178">
-        <v>1</v>
-      </c>
-      <c r="Y178">
-        <v>1</v>
-      </c>
-      <c r="Z178">
-        <v>1</v>
-      </c>
-      <c r="AA178">
+      <c r="P178">
+        <v>1</v>
+      </c>
+      <c r="Q178">
+        <v>1</v>
+      </c>
+      <c r="R178">
+        <v>1</v>
+      </c>
+      <c r="S178">
+        <v>1</v>
+      </c>
+      <c r="T178">
+        <v>1</v>
+      </c>
+      <c r="U178">
         <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:27">
       <c r="A179" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -13913,225 +14118,370 @@
     </row>
     <row r="180" spans="1:27">
       <c r="A180" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C180">
         <v>1</v>
       </c>
-      <c r="E180">
+      <c r="V180">
+        <v>1</v>
+      </c>
+      <c r="W180">
+        <v>1</v>
+      </c>
+      <c r="X180">
+        <v>1</v>
+      </c>
+      <c r="Y180">
+        <v>1</v>
+      </c>
+      <c r="Z180">
+        <v>1</v>
+      </c>
+      <c r="AA180">
         <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:27">
       <c r="A181" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C181">
         <v>1</v>
       </c>
-      <c r="F181">
+      <c r="V181">
+        <v>1</v>
+      </c>
+      <c r="W181">
+        <v>1</v>
+      </c>
+      <c r="X181">
+        <v>1</v>
+      </c>
+      <c r="Y181">
+        <v>1</v>
+      </c>
+      <c r="Z181">
+        <v>1</v>
+      </c>
+      <c r="AA181">
         <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:27">
       <c r="A182" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
-      <c r="H182">
+      <c r="V182">
+        <v>1</v>
+      </c>
+      <c r="W182">
+        <v>1</v>
+      </c>
+      <c r="X182">
+        <v>1</v>
+      </c>
+      <c r="Y182">
+        <v>1</v>
+      </c>
+      <c r="Z182">
+        <v>1</v>
+      </c>
+      <c r="AA182">
         <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:27">
       <c r="A183" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
-      <c r="I183">
+      <c r="V183">
+        <v>1</v>
+      </c>
+      <c r="W183">
+        <v>1</v>
+      </c>
+      <c r="X183">
+        <v>1</v>
+      </c>
+      <c r="Y183">
+        <v>1</v>
+      </c>
+      <c r="Z183">
+        <v>1</v>
+      </c>
+      <c r="AA183">
         <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:27">
       <c r="A184" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C184">
         <v>1</v>
       </c>
-      <c r="K184">
+      <c r="V184">
+        <v>1</v>
+      </c>
+      <c r="W184">
+        <v>1</v>
+      </c>
+      <c r="X184">
+        <v>1</v>
+      </c>
+      <c r="Y184">
+        <v>1</v>
+      </c>
+      <c r="Z184">
+        <v>1</v>
+      </c>
+      <c r="AA184">
         <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:27">
       <c r="A185" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C185">
         <v>1</v>
       </c>
-      <c r="L185">
+      <c r="E185">
         <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:27">
       <c r="A186" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C186">
         <v>1</v>
       </c>
-      <c r="N186">
+      <c r="F186">
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:27">
       <c r="A187" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
-      <c r="O187">
+      <c r="H187">
         <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:27">
       <c r="A188" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
-      <c r="Q188">
+      <c r="I188">
         <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:27">
       <c r="A189" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C189">
         <v>1</v>
       </c>
-      <c r="R189">
+      <c r="K189">
         <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:27">
       <c r="A190" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C190">
         <v>1</v>
       </c>
-      <c r="T190">
+      <c r="L190">
         <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:27">
       <c r="A191" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
-      <c r="U191">
+      <c r="N191">
         <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:27">
       <c r="A192" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
-      <c r="W192">
+      <c r="O192">
         <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:27">
       <c r="A193" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
-      <c r="X193">
+      <c r="Q193">
         <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:27">
       <c r="A194" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
-      <c r="Z194">
+      <c r="R194">
         <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:27">
       <c r="A195" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B195" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195">
+        <v>1</v>
+      </c>
+      <c r="T195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:27">
+      <c r="A196" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+      <c r="U196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:27">
+      <c r="A197" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="W197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:27">
+      <c r="A198" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C198">
+        <v>1</v>
+      </c>
+      <c r="X198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:27">
+      <c r="A199" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+      <c r="Z199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:27">
+      <c r="A200" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C195">
-        <v>1</v>
-      </c>
-      <c r="AA195">
+      <c r="C200">
+        <v>1</v>
+      </c>
+      <c r="AA200">
         <v>1</v>
       </c>
     </row>

--- a/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
+++ b/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
@@ -154,6 +154,9 @@
     <t>hep_dth</t>
   </si>
   <si>
+    <t>imig_prev</t>
+  </si>
+  <si>
     <t>imig_vax_prop</t>
   </si>
   <si>
@@ -302,9 +305,6 @@
   </si>
   <si>
     <t>emig_rate</t>
-  </si>
-  <si>
-    <t>imig_prev</t>
   </si>
   <si>
     <t>imig_rem</t>
@@ -1909,73 +1909,73 @@
         <v>1</v>
       </c>
       <c r="D13">
-        <v>0.1874999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1.1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0.75</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
         <v>0.9</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>0.1775390625</v>
-      </c>
-      <c r="H13">
-        <v>0.5499999999999999</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>0.6937500000000001</v>
-      </c>
-      <c r="K13">
-        <v>0.1242187499999999</v>
-      </c>
-      <c r="L13">
-        <v>1.1125</v>
-      </c>
-      <c r="M13">
-        <v>2.85722770690918</v>
-      </c>
-      <c r="N13">
-        <v>0.5249999999999999</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
       <c r="P13">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="Q13">
+        <v>1.05</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
         <v>0.9</v>
       </c>
-      <c r="R13">
-        <v>1</v>
-      </c>
-      <c r="S13">
-        <v>1</v>
-      </c>
-      <c r="T13">
+      <c r="W13">
         <v>0.9</v>
       </c>
-      <c r="U13">
-        <v>1</v>
-      </c>
-      <c r="V13">
-        <v>0.1</v>
-      </c>
-      <c r="W13">
-        <v>0.575</v>
-      </c>
       <c r="X13">
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z13">
-        <v>0.2374999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="AA13">
         <v>1</v>
@@ -3286,76 +3286,76 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="L30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="N30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="O30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="P30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="Q30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="R30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="S30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="T30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="U30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="V30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="W30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="X30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="Z30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="AA30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -3367,76 +3367,76 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>3.762171875000001</v>
       </c>
       <c r="M31">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>1.8125</v>
       </c>
       <c r="O31">
-        <v>1</v>
+        <v>2.940781250000001</v>
       </c>
       <c r="P31">
-        <v>1</v>
+        <v>1.331</v>
       </c>
       <c r="Q31">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="R31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T31">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="U31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="W31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AA31">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -4663,7 +4663,7 @@
         <v>1</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -4672,13 +4672,13 @@
         <v>1</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0.1874999999999999</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -4699,16 +4699,16 @@
         <v>1</v>
       </c>
       <c r="P47">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q47">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R47">
         <v>1</v>
       </c>
       <c r="S47">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T47">
         <v>1</v>
@@ -4717,7 +4717,7 @@
         <v>1</v>
       </c>
       <c r="V47">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W47">
         <v>1</v>
@@ -4732,7 +4732,7 @@
         <v>1</v>
       </c>
       <c r="AA47">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4744,76 +4744,76 @@
         <v>1</v>
       </c>
       <c r="D48">
-        <v>0.07784846305847154</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>2.347647125990987</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>0.03569866733551025</v>
+        <v>0.9</v>
       </c>
       <c r="H48">
-        <v>0.94388671875</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>10</v>
+        <v>1.21</v>
       </c>
       <c r="J48">
-        <v>1.49325927734375</v>
+        <v>1</v>
       </c>
       <c r="K48">
-        <v>6.784080180466175</v>
+        <v>1</v>
       </c>
       <c r="L48">
-        <v>1.797608623504639</v>
+        <v>1</v>
       </c>
       <c r="M48">
-        <v>0.8387500000000001</v>
+        <v>0.9</v>
       </c>
       <c r="N48">
-        <v>4.190825419127941</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O48">
-        <v>1.804707641601563</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P48">
-        <v>1.191767578125</v>
+        <v>1</v>
       </c>
       <c r="Q48">
-        <v>7.376191635131836</v>
+        <v>0.9</v>
       </c>
       <c r="R48">
-        <v>1.568143908441438</v>
+        <v>0.75</v>
       </c>
       <c r="S48">
-        <v>0.76796875</v>
+        <v>1</v>
       </c>
       <c r="T48">
-        <v>4.475347220897674</v>
+        <v>1</v>
       </c>
       <c r="U48">
-        <v>1.725154495239258</v>
+        <v>0.75</v>
       </c>
       <c r="V48">
-        <v>1.6812744140625</v>
+        <v>1</v>
       </c>
       <c r="W48">
-        <v>10</v>
+        <v>0.675</v>
       </c>
       <c r="X48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>0.9975000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="Z48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AA48">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4825,76 +4825,76 @@
         <v>1</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0.5774999999999999</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>0.5249999999999999</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>1.99375</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0.7875</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>1.93875</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>0.1687499999999999</v>
       </c>
       <c r="M49">
-        <v>1</v>
+        <v>0.2062499999999999</v>
       </c>
       <c r="N49">
-        <v>1</v>
+        <v>0.5774999999999999</v>
       </c>
       <c r="O49">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P49">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q49">
-        <v>1</v>
+        <v>0.3906249999999999</v>
       </c>
       <c r="R49">
-        <v>1</v>
+        <v>0.9450000000000001</v>
       </c>
       <c r="S49">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="T49">
-        <v>1</v>
+        <v>0.675</v>
       </c>
       <c r="U49">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="V49">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="W49">
-        <v>1</v>
+        <v>0.6168749999999998</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="Y49">
-        <v>1</v>
+        <v>0.4725</v>
       </c>
       <c r="Z49">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="AA49">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -6544,28 +6544,28 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="K70">
         <v>1</v>
       </c>
       <c r="L70">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="M70">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N70">
         <v>1</v>
       </c>
       <c r="O70">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P70">
         <v>1</v>
       </c>
       <c r="Q70">
-        <v>0.9500000000000001</v>
+        <v>1</v>
       </c>
       <c r="R70">
         <v>1</v>
@@ -6574,7 +6574,7 @@
         <v>1</v>
       </c>
       <c r="T70">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U70">
         <v>1</v>
@@ -6583,16 +6583,16 @@
         <v>1</v>
       </c>
       <c r="W70">
-        <v>0.825</v>
+        <v>1</v>
       </c>
       <c r="X70">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y70">
         <v>1</v>
       </c>
       <c r="Z70">
-        <v>1.15625</v>
+        <v>1</v>
       </c>
       <c r="AA70">
         <v>1</v>
@@ -6625,28 +6625,28 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K71">
         <v>1</v>
       </c>
       <c r="L71">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="M71">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N71">
         <v>1</v>
       </c>
       <c r="O71">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="P71">
         <v>1</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>0.1874999999999999</v>
       </c>
       <c r="R71">
         <v>1</v>
@@ -6655,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="T71">
-        <v>1</v>
+        <v>1.475</v>
       </c>
       <c r="U71">
         <v>1</v>
@@ -6664,7 +6664,7 @@
         <v>1</v>
       </c>
       <c r="W71">
-        <v>1</v>
+        <v>0.5249999999999999</v>
       </c>
       <c r="X71">
         <v>1</v>
@@ -6673,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="Z71">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AA71">
         <v>1</v>
@@ -7660,7 +7660,7 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E84">
         <v>1</v>
@@ -7672,10 +7672,10 @@
         <v>1</v>
       </c>
       <c r="H84">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I84">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J84">
         <v>1</v>
@@ -7684,10 +7684,10 @@
         <v>1</v>
       </c>
       <c r="L84">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M84">
-        <v>1</v>
+        <v>0.675</v>
       </c>
       <c r="N84">
         <v>1</v>
@@ -7696,13 +7696,13 @@
         <v>1</v>
       </c>
       <c r="P84">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q84">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R84">
-        <v>1</v>
+        <v>0.5249999999999999</v>
       </c>
       <c r="S84">
         <v>1</v>
@@ -7711,16 +7711,16 @@
         <v>1</v>
       </c>
       <c r="U84">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="V84">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W84">
         <v>1</v>
       </c>
       <c r="X84">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y84">
         <v>1</v>
@@ -7729,7 +7729,7 @@
         <v>1</v>
       </c>
       <c r="AA84">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="85" spans="1:27">
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J85">
         <v>1</v>
@@ -7765,7 +7765,7 @@
         <v>1</v>
       </c>
       <c r="L85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85">
         <v>1</v>
@@ -7774,16 +7774,16 @@
         <v>1</v>
       </c>
       <c r="O85">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P85">
         <v>1</v>
       </c>
       <c r="Q85">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R85">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S85">
         <v>1</v>

--- a/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
+++ b/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
@@ -154,6 +154,9 @@
     <t>hep_dth</t>
   </si>
   <si>
+    <t>imig_prev</t>
+  </si>
+  <si>
     <t>imig_vax_prop</t>
   </si>
   <si>
@@ -302,9 +305,6 @@
   </si>
   <si>
     <t>emig_rate</t>
-  </si>
-  <si>
-    <t>imig_prev</t>
   </si>
   <si>
     <t>imig_rem</t>
@@ -3286,76 +3286,76 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="L30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="N30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="O30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="P30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="Q30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="R30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="S30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="T30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="U30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="V30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="W30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="X30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="Z30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="AA30">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -3367,76 +3367,76 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="M31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="O31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="P31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="Q31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="R31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="S31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="T31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="U31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="V31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="W31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="Y31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="Z31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="AA31">
-        <v>1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -4663,70 +4663,70 @@
         <v>1</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>1.475</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>0.1874999999999999</v>
       </c>
       <c r="K47">
         <v>1</v>
       </c>
       <c r="L47">
-        <v>1</v>
+        <v>0.2874999999999999</v>
       </c>
       <c r="M47">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O47">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="P47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47">
         <v>1</v>
       </c>
       <c r="T47">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="U47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="W47">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z47">
         <v>1</v>
@@ -4744,76 +4744,76 @@
         <v>1</v>
       </c>
       <c r="D48">
-        <v>0.07784846305847154</v>
+        <v>0.5249999999999999</v>
       </c>
       <c r="E48">
-        <v>2.347647125990987</v>
+        <v>0.9</v>
       </c>
       <c r="F48">
-        <v>10</v>
+        <v>1.25</v>
       </c>
       <c r="G48">
-        <v>0.03569866733551025</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>0.94388671875</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J48">
-        <v>1.49325927734375</v>
+        <v>1</v>
       </c>
       <c r="K48">
-        <v>6.784080180466175</v>
+        <v>0.75</v>
       </c>
       <c r="L48">
-        <v>1.797608623504639</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>0.8387500000000001</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>4.190825419127941</v>
+        <v>1</v>
       </c>
       <c r="O48">
-        <v>1.804707641601563</v>
+        <v>1</v>
       </c>
       <c r="P48">
-        <v>1.191767578125</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>7.376191635131836</v>
+        <v>0.9</v>
       </c>
       <c r="R48">
-        <v>1.568143908441438</v>
+        <v>0.6249999999999999</v>
       </c>
       <c r="S48">
-        <v>0.76796875</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>4.475347220897674</v>
+        <v>0.9</v>
       </c>
       <c r="U48">
-        <v>1.725154495239258</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>1.6812744140625</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X48">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y48">
-        <v>0.9975000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z48">
-        <v>10</v>
+        <v>0.9</v>
       </c>
       <c r="AA48">
-        <v>10</v>
+        <v>0.1874999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4825,76 +4825,76 @@
         <v>1</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="M49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="N49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="O49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="P49">
-        <v>1</v>
+        <v>0.04008109247684479</v>
       </c>
       <c r="Q49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="R49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="S49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="U49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="V49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="AA49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -6544,28 +6544,28 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="K70">
         <v>1</v>
       </c>
       <c r="L70">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="M70">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N70">
         <v>1</v>
       </c>
       <c r="O70">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P70">
         <v>1</v>
       </c>
       <c r="Q70">
-        <v>0.9500000000000001</v>
+        <v>1</v>
       </c>
       <c r="R70">
         <v>1</v>
@@ -6574,7 +6574,7 @@
         <v>1</v>
       </c>
       <c r="T70">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U70">
         <v>1</v>
@@ -6583,16 +6583,16 @@
         <v>1</v>
       </c>
       <c r="W70">
-        <v>0.825</v>
+        <v>1</v>
       </c>
       <c r="X70">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y70">
         <v>1</v>
       </c>
       <c r="Z70">
-        <v>1.15625</v>
+        <v>1</v>
       </c>
       <c r="AA70">
         <v>1</v>
@@ -6625,28 +6625,28 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K71">
         <v>1</v>
       </c>
       <c r="L71">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="M71">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N71">
         <v>1</v>
       </c>
       <c r="O71">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P71">
         <v>1</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="R71">
         <v>1</v>
@@ -6655,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="T71">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U71">
         <v>1</v>
@@ -6664,16 +6664,16 @@
         <v>1</v>
       </c>
       <c r="W71">
-        <v>1</v>
+        <v>0.825</v>
       </c>
       <c r="X71">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y71">
         <v>1</v>
       </c>
       <c r="Z71">
-        <v>1</v>
+        <v>1.15625</v>
       </c>
       <c r="AA71">
         <v>1</v>
@@ -7660,46 +7660,46 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J84">
-        <v>1</v>
+        <v>0.5249999999999999</v>
       </c>
       <c r="K84">
-        <v>1</v>
+        <v>0.1874999999999999</v>
       </c>
       <c r="L84">
         <v>1</v>
       </c>
       <c r="M84">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="N84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84">
         <v>1</v>
@@ -7708,28 +7708,28 @@
         <v>1</v>
       </c>
       <c r="T84">
-        <v>1</v>
+        <v>0.1874999999999999</v>
       </c>
       <c r="U84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V84">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W84">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X84">
         <v>1</v>
       </c>
       <c r="Y84">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Z84">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AA84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:27">
@@ -7744,19 +7744,19 @@
         <v>1</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>0.5249999999999999</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85">
         <v>1</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85">
         <v>1</v>
@@ -7765,13 +7765,13 @@
         <v>1</v>
       </c>
       <c r="L85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85">
         <v>1</v>
       </c>
       <c r="N85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85">
         <v>1</v>
@@ -7780,10 +7780,10 @@
         <v>1</v>
       </c>
       <c r="Q85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>1</v>
+        <v>0.1874999999999999</v>
       </c>
       <c r="S85">
         <v>1</v>
@@ -7792,16 +7792,16 @@
         <v>1</v>
       </c>
       <c r="U85">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="V85">
         <v>1</v>
       </c>
       <c r="W85">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="X85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y85">
         <v>1</v>
@@ -7810,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="AA85">
-        <v>1</v>
+        <v>0.5249999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:27">

--- a/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
+++ b/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="218">
   <si>
     <t>meta_y_factor</t>
   </si>
@@ -301,6 +301,54 @@
     <t>treat_measure</t>
   </si>
   <si>
+    <t>disc_rate_cost</t>
+  </si>
+  <si>
+    <t>diag_price</t>
+  </si>
+  <si>
+    <t>chb_ltc_price</t>
+  </si>
+  <si>
+    <t>cc_ltc_price</t>
+  </si>
+  <si>
+    <t>dc_ltc_nt_price</t>
+  </si>
+  <si>
+    <t>dc_ltc_tx_price</t>
+  </si>
+  <si>
+    <t>hcc_ltc_nt_price</t>
+  </si>
+  <si>
+    <t>hcc_ltc_tx_price</t>
+  </si>
+  <si>
+    <t>treat_price</t>
+  </si>
+  <si>
+    <t>stat_year_life</t>
+  </si>
+  <si>
+    <t>ql_clr</t>
+  </si>
+  <si>
+    <t>ql_chb</t>
+  </si>
+  <si>
+    <t>ql_cc</t>
+  </si>
+  <si>
+    <t>ql_dc</t>
+  </si>
+  <si>
+    <t>ql_hcc</t>
+  </si>
+  <si>
+    <t>disc_rate_qaly</t>
+  </si>
+  <si>
     <t>imig_rate</t>
   </si>
   <si>
@@ -547,6 +595,12 @@
     <t>horiz</t>
   </si>
   <si>
+    <t>horiz_chb</t>
+  </si>
+  <si>
+    <t>horiz_acu</t>
+  </si>
+  <si>
     <t>diag_rate</t>
   </si>
   <si>
@@ -557,6 +611,54 @@
   </si>
   <si>
     <t>inc_hcc</t>
+  </si>
+  <si>
+    <t>diagnoses</t>
+  </si>
+  <si>
+    <t>diag_cost</t>
+  </si>
+  <si>
+    <t>chb_dm_cost</t>
+  </si>
+  <si>
+    <t>cc_dm_cost</t>
+  </si>
+  <si>
+    <t>dc_dm_cost</t>
+  </si>
+  <si>
+    <t>hcc_dm_cost</t>
+  </si>
+  <si>
+    <t>dm_cost</t>
+  </si>
+  <si>
+    <t>treat_cost</t>
+  </si>
+  <si>
+    <t>direct_costs</t>
+  </si>
+  <si>
+    <t>mort_cost</t>
+  </si>
+  <si>
+    <t>qalys_clr</t>
+  </si>
+  <si>
+    <t>qalys_chb</t>
+  </si>
+  <si>
+    <t>qalys_cc</t>
+  </si>
+  <si>
+    <t>qalys_dc</t>
+  </si>
+  <si>
+    <t>qalys_hcc</t>
+  </si>
+  <si>
+    <t>qalys_total</t>
   </si>
   <si>
     <t>mx_mtct</t>
@@ -923,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA200"/>
+  <dimension ref="A1:AA234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
@@ -4663,40 +4765,40 @@
         <v>1</v>
       </c>
       <c r="D47">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>1.475</v>
+        <v>5</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0.9500000000000001</v>
+        <v>5</v>
       </c>
       <c r="J47">
-        <v>0.1874999999999999</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47">
-        <v>0.2874999999999999</v>
+        <v>1.19447265625</v>
       </c>
       <c r="M47">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="N47">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>0.75</v>
+        <v>0.7985742187499999</v>
       </c>
       <c r="P47">
         <v>0</v>
@@ -4705,34 +4807,34 @@
         <v>0</v>
       </c>
       <c r="R47">
+        <v>0.1823400297619048</v>
+      </c>
+      <c r="S47">
         <v>0</v>
       </c>
-      <c r="S47">
-        <v>1</v>
-      </c>
       <c r="T47">
-        <v>0.75</v>
+        <v>0.24345703125</v>
       </c>
       <c r="U47">
+        <v>0.4051450117807538</v>
+      </c>
+      <c r="V47">
         <v>0</v>
       </c>
-      <c r="V47">
-        <v>0.75</v>
-      </c>
       <c r="W47">
-        <v>0.9</v>
+        <v>0.4725</v>
       </c>
       <c r="X47">
-        <v>0.9</v>
+        <v>0.855</v>
       </c>
       <c r="Y47">
         <v>0</v>
       </c>
       <c r="Z47">
-        <v>1</v>
+        <v>0.0525</v>
       </c>
       <c r="AA47">
-        <v>1</v>
+        <v>0.9506249999999999</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4744,28 +4846,28 @@
         <v>1</v>
       </c>
       <c r="D48">
-        <v>0.5249999999999999</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>0.9</v>
+        <v>0.5338586425781251</v>
       </c>
       <c r="F48">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0.60703125</v>
       </c>
       <c r="I48">
+        <v>5</v>
+      </c>
+      <c r="J48">
         <v>0</v>
       </c>
-      <c r="J48">
-        <v>1</v>
-      </c>
       <c r="K48">
-        <v>0.75</v>
+        <v>0.497900390625</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4774,28 +4876,28 @@
         <v>0</v>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>0.5362499999999999</v>
       </c>
       <c r="O48">
-        <v>1</v>
+        <v>0.5012109374999999</v>
       </c>
       <c r="P48">
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0.9</v>
+        <v>0.1908976135253907</v>
       </c>
       <c r="R48">
-        <v>0.6249999999999999</v>
+        <v>1.390847778320313</v>
       </c>
       <c r="S48">
         <v>0</v>
       </c>
       <c r="T48">
-        <v>0.9</v>
+        <v>0.163740234375</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>0.9250176980909374</v>
       </c>
       <c r="V48">
         <v>0</v>
@@ -4810,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="Z48">
-        <v>0.9</v>
+        <v>0.16875</v>
       </c>
       <c r="AA48">
-        <v>0.1874999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4861,7 +4963,7 @@
         <v>0.05</v>
       </c>
       <c r="P49">
-        <v>0.04008109247684479</v>
+        <v>0.05</v>
       </c>
       <c r="Q49">
         <v>0.05</v>
@@ -6625,28 +6727,28 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="K71">
         <v>1</v>
       </c>
       <c r="L71">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="M71">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N71">
         <v>1</v>
       </c>
       <c r="O71">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P71">
         <v>1</v>
       </c>
       <c r="Q71">
-        <v>0.9500000000000001</v>
+        <v>1</v>
       </c>
       <c r="R71">
         <v>1</v>
@@ -6655,7 +6757,7 @@
         <v>1</v>
       </c>
       <c r="T71">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U71">
         <v>1</v>
@@ -6664,16 +6766,16 @@
         <v>1</v>
       </c>
       <c r="W71">
-        <v>0.825</v>
+        <v>1</v>
       </c>
       <c r="X71">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y71">
         <v>1</v>
       </c>
       <c r="Z71">
-        <v>1.15625</v>
+        <v>1</v>
       </c>
       <c r="AA71">
         <v>1</v>
@@ -7660,46 +7762,46 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J84">
-        <v>0.5249999999999999</v>
+        <v>1</v>
       </c>
       <c r="K84">
-        <v>0.1874999999999999</v>
+        <v>1</v>
       </c>
       <c r="L84">
         <v>1</v>
       </c>
       <c r="M84">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84">
         <v>1</v>
@@ -7708,28 +7810,28 @@
         <v>1</v>
       </c>
       <c r="T84">
-        <v>0.1874999999999999</v>
+        <v>1</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V84">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W84">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X84">
         <v>1</v>
       </c>
       <c r="Y84">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="Z84">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:27">
@@ -7744,19 +7846,19 @@
         <v>1</v>
       </c>
       <c r="E85">
-        <v>0.5249999999999999</v>
+        <v>1</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85">
         <v>1</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85">
         <v>1</v>
@@ -7765,13 +7867,13 @@
         <v>1</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85">
         <v>1</v>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85">
         <v>1</v>
@@ -7780,10 +7882,10 @@
         <v>1</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85">
-        <v>0.1874999999999999</v>
+        <v>1</v>
       </c>
       <c r="S85">
         <v>1</v>
@@ -7792,16 +7894,16 @@
         <v>1</v>
       </c>
       <c r="U85">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V85">
         <v>1</v>
       </c>
       <c r="W85">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y85">
         <v>1</v>
@@ -7810,7 +7912,7 @@
         <v>1</v>
       </c>
       <c r="AA85">
-        <v>0.5249999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:27">
@@ -7921,28 +8023,28 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K87">
         <v>1</v>
       </c>
       <c r="L87">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="M87">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N87">
         <v>1</v>
       </c>
       <c r="O87">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P87">
         <v>1</v>
       </c>
       <c r="Q87">
-        <v>1</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="R87">
         <v>1</v>
@@ -7951,7 +8053,7 @@
         <v>1</v>
       </c>
       <c r="T87">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U87">
         <v>1</v>
@@ -7960,16 +8062,16 @@
         <v>1</v>
       </c>
       <c r="W87">
-        <v>1</v>
+        <v>0.825</v>
       </c>
       <c r="X87">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y87">
         <v>1</v>
       </c>
       <c r="Z87">
-        <v>1</v>
+        <v>1.15625</v>
       </c>
       <c r="AA87">
         <v>1</v>
@@ -8956,76 +9058,76 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>0.6639597089471153</v>
       </c>
       <c r="I100">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100">
-        <v>1</v>
+        <v>2.722714198835427</v>
       </c>
       <c r="L100">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q100">
-        <v>1</v>
+        <v>4.231301884319995</v>
       </c>
       <c r="R100">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U100">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W100">
-        <v>1</v>
+        <v>0.730078125</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z100">
-        <v>1</v>
+        <v>0.309375</v>
       </c>
       <c r="AA100">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:27">
@@ -9040,73 +9142,73 @@
         <v>1</v>
       </c>
       <c r="E101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G101">
         <v>1</v>
       </c>
       <c r="H101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J101">
         <v>1</v>
       </c>
       <c r="K101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101">
         <v>1</v>
       </c>
       <c r="N101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P101">
         <v>1</v>
       </c>
       <c r="Q101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S101">
         <v>1</v>
       </c>
       <c r="T101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V101">
         <v>1</v>
       </c>
       <c r="W101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y101">
         <v>1</v>
       </c>
       <c r="Z101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA101">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:27">
@@ -13487,91 +13589,412 @@
       <c r="A156" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B156" s="1"/>
       <c r="C156">
         <v>1</v>
       </c>
       <c r="D156">
+        <v>1</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156">
+        <v>1</v>
+      </c>
+      <c r="H156">
+        <v>1</v>
+      </c>
+      <c r="I156">
+        <v>1</v>
+      </c>
+      <c r="J156">
+        <v>1</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156">
+        <v>1</v>
+      </c>
+      <c r="M156">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>1</v>
+      </c>
+      <c r="O156">
+        <v>1</v>
+      </c>
+      <c r="P156">
+        <v>1</v>
+      </c>
+      <c r="Q156">
+        <v>1</v>
+      </c>
+      <c r="R156">
+        <v>1</v>
+      </c>
+      <c r="S156">
+        <v>1</v>
+      </c>
+      <c r="T156">
+        <v>1</v>
+      </c>
+      <c r="U156">
+        <v>1</v>
+      </c>
+      <c r="V156">
+        <v>1</v>
+      </c>
+      <c r="W156">
+        <v>1</v>
+      </c>
+      <c r="X156">
+        <v>1</v>
+      </c>
+      <c r="Y156">
+        <v>1</v>
+      </c>
+      <c r="Z156">
+        <v>1</v>
+      </c>
+      <c r="AA156">
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:27">
       <c r="A157" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="B157" s="1"/>
       <c r="C157">
         <v>1</v>
       </c>
       <c r="D157">
         <v>1</v>
       </c>
+      <c r="E157">
+        <v>1</v>
+      </c>
+      <c r="F157">
+        <v>1</v>
+      </c>
       <c r="G157">
+        <v>1</v>
+      </c>
+      <c r="H157">
+        <v>1</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
+      <c r="J157">
+        <v>1</v>
+      </c>
+      <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="L157">
+        <v>1</v>
+      </c>
+      <c r="M157">
+        <v>1</v>
+      </c>
+      <c r="N157">
+        <v>1</v>
+      </c>
+      <c r="O157">
+        <v>1</v>
+      </c>
+      <c r="P157">
+        <v>1</v>
+      </c>
+      <c r="Q157">
+        <v>1</v>
+      </c>
+      <c r="R157">
+        <v>1</v>
+      </c>
+      <c r="S157">
+        <v>1</v>
+      </c>
+      <c r="T157">
+        <v>1</v>
+      </c>
+      <c r="U157">
+        <v>1</v>
+      </c>
+      <c r="V157">
+        <v>1</v>
+      </c>
+      <c r="W157">
+        <v>1</v>
+      </c>
+      <c r="X157">
+        <v>1</v>
+      </c>
+      <c r="Y157">
+        <v>1</v>
+      </c>
+      <c r="Z157">
+        <v>1</v>
+      </c>
+      <c r="AA157">
         <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:27">
       <c r="A158" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="B158" s="1"/>
       <c r="C158">
         <v>1</v>
       </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+      <c r="H158">
+        <v>1</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
       <c r="J158">
         <v>1</v>
       </c>
+      <c r="K158">
+        <v>1</v>
+      </c>
+      <c r="L158">
+        <v>1</v>
+      </c>
       <c r="M158">
+        <v>1</v>
+      </c>
+      <c r="N158">
+        <v>1</v>
+      </c>
+      <c r="O158">
+        <v>1</v>
+      </c>
+      <c r="P158">
+        <v>1</v>
+      </c>
+      <c r="Q158">
+        <v>1</v>
+      </c>
+      <c r="R158">
+        <v>1</v>
+      </c>
+      <c r="S158">
+        <v>1</v>
+      </c>
+      <c r="T158">
+        <v>1</v>
+      </c>
+      <c r="U158">
+        <v>1</v>
+      </c>
+      <c r="V158">
+        <v>1</v>
+      </c>
+      <c r="W158">
+        <v>1</v>
+      </c>
+      <c r="X158">
+        <v>1</v>
+      </c>
+      <c r="Y158">
+        <v>1</v>
+      </c>
+      <c r="Z158">
+        <v>1</v>
+      </c>
+      <c r="AA158">
         <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:27">
       <c r="A159" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="B159" s="1"/>
       <c r="C159">
         <v>1</v>
       </c>
+      <c r="D159">
+        <v>1</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+      <c r="H159">
+        <v>1</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
       <c r="J159">
         <v>1</v>
       </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+      <c r="L159">
+        <v>1</v>
+      </c>
       <c r="M159">
+        <v>1</v>
+      </c>
+      <c r="N159">
+        <v>1</v>
+      </c>
+      <c r="O159">
+        <v>1</v>
+      </c>
+      <c r="P159">
+        <v>1</v>
+      </c>
+      <c r="Q159">
+        <v>1</v>
+      </c>
+      <c r="R159">
+        <v>1</v>
+      </c>
+      <c r="S159">
+        <v>1</v>
+      </c>
+      <c r="T159">
+        <v>1</v>
+      </c>
+      <c r="U159">
+        <v>1</v>
+      </c>
+      <c r="V159">
+        <v>1</v>
+      </c>
+      <c r="W159">
+        <v>1</v>
+      </c>
+      <c r="X159">
+        <v>1</v>
+      </c>
+      <c r="Y159">
+        <v>1</v>
+      </c>
+      <c r="Z159">
+        <v>1</v>
+      </c>
+      <c r="AA159">
         <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:27">
       <c r="A160" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="B160" s="1"/>
       <c r="C160">
         <v>1</v>
       </c>
+      <c r="D160">
+        <v>1</v>
+      </c>
+      <c r="E160">
+        <v>1</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160">
+        <v>1</v>
+      </c>
+      <c r="H160">
+        <v>1</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
       <c r="J160">
         <v>1</v>
       </c>
+      <c r="K160">
+        <v>1</v>
+      </c>
+      <c r="L160">
+        <v>1</v>
+      </c>
       <c r="M160">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:21">
+      <c r="N160">
+        <v>1</v>
+      </c>
+      <c r="O160">
+        <v>1</v>
+      </c>
+      <c r="P160">
+        <v>1</v>
+      </c>
+      <c r="Q160">
+        <v>1</v>
+      </c>
+      <c r="R160">
+        <v>1</v>
+      </c>
+      <c r="S160">
+        <v>1</v>
+      </c>
+      <c r="T160">
+        <v>1</v>
+      </c>
+      <c r="U160">
+        <v>1</v>
+      </c>
+      <c r="V160">
+        <v>1</v>
+      </c>
+      <c r="W160">
+        <v>1</v>
+      </c>
+      <c r="X160">
+        <v>1</v>
+      </c>
+      <c r="Y160">
+        <v>1</v>
+      </c>
+      <c r="Z160">
+        <v>1</v>
+      </c>
+      <c r="AA160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:27">
       <c r="A161" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>1</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="B161" s="1"/>
       <c r="C161">
         <v>1</v>
       </c>
@@ -13593,14 +14016,66 @@
       <c r="I161">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:21">
+      <c r="J161">
+        <v>1</v>
+      </c>
+      <c r="K161">
+        <v>1</v>
+      </c>
+      <c r="L161">
+        <v>1</v>
+      </c>
+      <c r="M161">
+        <v>1</v>
+      </c>
+      <c r="N161">
+        <v>1</v>
+      </c>
+      <c r="O161">
+        <v>1</v>
+      </c>
+      <c r="P161">
+        <v>1</v>
+      </c>
+      <c r="Q161">
+        <v>1</v>
+      </c>
+      <c r="R161">
+        <v>1</v>
+      </c>
+      <c r="S161">
+        <v>1</v>
+      </c>
+      <c r="T161">
+        <v>1</v>
+      </c>
+      <c r="U161">
+        <v>1</v>
+      </c>
+      <c r="V161">
+        <v>1</v>
+      </c>
+      <c r="W161">
+        <v>1</v>
+      </c>
+      <c r="X161">
+        <v>1</v>
+      </c>
+      <c r="Y161">
+        <v>1</v>
+      </c>
+      <c r="Z161">
+        <v>1</v>
+      </c>
+      <c r="AA161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:27">
       <c r="A162" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="B162" s="1"/>
       <c r="C162">
         <v>1</v>
       </c>
@@ -13622,14 +14097,66 @@
       <c r="I162">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:21">
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162">
+        <v>1</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>1</v>
+      </c>
+      <c r="O162">
+        <v>1</v>
+      </c>
+      <c r="P162">
+        <v>1</v>
+      </c>
+      <c r="Q162">
+        <v>1</v>
+      </c>
+      <c r="R162">
+        <v>1</v>
+      </c>
+      <c r="S162">
+        <v>1</v>
+      </c>
+      <c r="T162">
+        <v>1</v>
+      </c>
+      <c r="U162">
+        <v>1</v>
+      </c>
+      <c r="V162">
+        <v>1</v>
+      </c>
+      <c r="W162">
+        <v>1</v>
+      </c>
+      <c r="X162">
+        <v>1</v>
+      </c>
+      <c r="Y162">
+        <v>1</v>
+      </c>
+      <c r="Z162">
+        <v>1</v>
+      </c>
+      <c r="AA162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:27">
       <c r="A163" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>3</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="B163" s="1"/>
       <c r="C163">
         <v>1</v>
       </c>
@@ -13651,14 +14178,66 @@
       <c r="I163">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:21">
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+      <c r="N163">
+        <v>1</v>
+      </c>
+      <c r="O163">
+        <v>1</v>
+      </c>
+      <c r="P163">
+        <v>1</v>
+      </c>
+      <c r="Q163">
+        <v>1</v>
+      </c>
+      <c r="R163">
+        <v>1</v>
+      </c>
+      <c r="S163">
+        <v>1</v>
+      </c>
+      <c r="T163">
+        <v>1</v>
+      </c>
+      <c r="U163">
+        <v>1</v>
+      </c>
+      <c r="V163">
+        <v>1</v>
+      </c>
+      <c r="W163">
+        <v>1</v>
+      </c>
+      <c r="X163">
+        <v>1</v>
+      </c>
+      <c r="Y163">
+        <v>1</v>
+      </c>
+      <c r="Z163">
+        <v>1</v>
+      </c>
+      <c r="AA163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:27">
       <c r="A164" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="B164" s="1"/>
       <c r="C164">
         <v>1</v>
       </c>
@@ -13680,14 +14259,66 @@
       <c r="I164">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:21">
+      <c r="J164">
+        <v>1</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="M164">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>1</v>
+      </c>
+      <c r="O164">
+        <v>1</v>
+      </c>
+      <c r="P164">
+        <v>1</v>
+      </c>
+      <c r="Q164">
+        <v>1</v>
+      </c>
+      <c r="R164">
+        <v>1</v>
+      </c>
+      <c r="S164">
+        <v>1</v>
+      </c>
+      <c r="T164">
+        <v>1</v>
+      </c>
+      <c r="U164">
+        <v>1</v>
+      </c>
+      <c r="V164">
+        <v>1</v>
+      </c>
+      <c r="W164">
+        <v>1</v>
+      </c>
+      <c r="X164">
+        <v>1</v>
+      </c>
+      <c r="Y164">
+        <v>1</v>
+      </c>
+      <c r="Z164">
+        <v>1</v>
+      </c>
+      <c r="AA164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:27">
       <c r="A165" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="B165" s="1"/>
       <c r="C165">
         <v>1</v>
       </c>
@@ -13709,14 +14340,66 @@
       <c r="I165">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:21">
+      <c r="J165">
+        <v>1</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="M165">
+        <v>1</v>
+      </c>
+      <c r="N165">
+        <v>1</v>
+      </c>
+      <c r="O165">
+        <v>1</v>
+      </c>
+      <c r="P165">
+        <v>1</v>
+      </c>
+      <c r="Q165">
+        <v>1</v>
+      </c>
+      <c r="R165">
+        <v>1</v>
+      </c>
+      <c r="S165">
+        <v>1</v>
+      </c>
+      <c r="T165">
+        <v>1</v>
+      </c>
+      <c r="U165">
+        <v>1</v>
+      </c>
+      <c r="V165">
+        <v>1</v>
+      </c>
+      <c r="W165">
+        <v>1</v>
+      </c>
+      <c r="X165">
+        <v>1</v>
+      </c>
+      <c r="Y165">
+        <v>1</v>
+      </c>
+      <c r="Z165">
+        <v>1</v>
+      </c>
+      <c r="AA165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:27">
       <c r="A166" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="B166" s="1"/>
       <c r="C166">
         <v>1</v>
       </c>
@@ -13738,17 +14421,87 @@
       <c r="I166">
         <v>1</v>
       </c>
-    </row>
-    <row r="167" spans="1:21">
+      <c r="J166">
+        <v>1</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="L166">
+        <v>1</v>
+      </c>
+      <c r="M166">
+        <v>1</v>
+      </c>
+      <c r="N166">
+        <v>1</v>
+      </c>
+      <c r="O166">
+        <v>1</v>
+      </c>
+      <c r="P166">
+        <v>1</v>
+      </c>
+      <c r="Q166">
+        <v>1</v>
+      </c>
+      <c r="R166">
+        <v>1</v>
+      </c>
+      <c r="S166">
+        <v>1</v>
+      </c>
+      <c r="T166">
+        <v>1</v>
+      </c>
+      <c r="U166">
+        <v>1</v>
+      </c>
+      <c r="V166">
+        <v>1</v>
+      </c>
+      <c r="W166">
+        <v>1</v>
+      </c>
+      <c r="X166">
+        <v>1</v>
+      </c>
+      <c r="Y166">
+        <v>1</v>
+      </c>
+      <c r="Z166">
+        <v>1</v>
+      </c>
+      <c r="AA166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:27">
       <c r="A167" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="B167" s="1"/>
       <c r="C167">
         <v>1</v>
       </c>
+      <c r="D167">
+        <v>1</v>
+      </c>
+      <c r="E167">
+        <v>1</v>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167">
+        <v>1</v>
+      </c>
+      <c r="H167">
+        <v>1</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
       <c r="J167">
         <v>1</v>
       </c>
@@ -13767,17 +14520,69 @@
       <c r="O167">
         <v>1</v>
       </c>
-    </row>
-    <row r="168" spans="1:21">
+      <c r="P167">
+        <v>1</v>
+      </c>
+      <c r="Q167">
+        <v>1</v>
+      </c>
+      <c r="R167">
+        <v>1</v>
+      </c>
+      <c r="S167">
+        <v>1</v>
+      </c>
+      <c r="T167">
+        <v>1</v>
+      </c>
+      <c r="U167">
+        <v>1</v>
+      </c>
+      <c r="V167">
+        <v>1</v>
+      </c>
+      <c r="W167">
+        <v>1</v>
+      </c>
+      <c r="X167">
+        <v>1</v>
+      </c>
+      <c r="Y167">
+        <v>1</v>
+      </c>
+      <c r="Z167">
+        <v>1</v>
+      </c>
+      <c r="AA167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:27">
       <c r="A168" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="B168" s="1"/>
       <c r="C168">
         <v>1</v>
       </c>
+      <c r="D168">
+        <v>1</v>
+      </c>
+      <c r="E168">
+        <v>1</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+      <c r="H168">
+        <v>1</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
       <c r="J168">
         <v>1</v>
       </c>
@@ -13796,17 +14601,69 @@
       <c r="O168">
         <v>1</v>
       </c>
-    </row>
-    <row r="169" spans="1:21">
+      <c r="P168">
+        <v>1</v>
+      </c>
+      <c r="Q168">
+        <v>1</v>
+      </c>
+      <c r="R168">
+        <v>1</v>
+      </c>
+      <c r="S168">
+        <v>1</v>
+      </c>
+      <c r="T168">
+        <v>1</v>
+      </c>
+      <c r="U168">
+        <v>1</v>
+      </c>
+      <c r="V168">
+        <v>1</v>
+      </c>
+      <c r="W168">
+        <v>1</v>
+      </c>
+      <c r="X168">
+        <v>1</v>
+      </c>
+      <c r="Y168">
+        <v>1</v>
+      </c>
+      <c r="Z168">
+        <v>1</v>
+      </c>
+      <c r="AA168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:27">
       <c r="A169" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="B169" s="1"/>
       <c r="C169">
         <v>1</v>
       </c>
+      <c r="D169">
+        <v>1</v>
+      </c>
+      <c r="E169">
+        <v>1</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169">
+        <v>1</v>
+      </c>
+      <c r="H169">
+        <v>1</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
       <c r="J169">
         <v>1</v>
       </c>
@@ -13825,17 +14682,69 @@
       <c r="O169">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:21">
+      <c r="P169">
+        <v>1</v>
+      </c>
+      <c r="Q169">
+        <v>1</v>
+      </c>
+      <c r="R169">
+        <v>1</v>
+      </c>
+      <c r="S169">
+        <v>1</v>
+      </c>
+      <c r="T169">
+        <v>1</v>
+      </c>
+      <c r="U169">
+        <v>1</v>
+      </c>
+      <c r="V169">
+        <v>1</v>
+      </c>
+      <c r="W169">
+        <v>1</v>
+      </c>
+      <c r="X169">
+        <v>1</v>
+      </c>
+      <c r="Y169">
+        <v>1</v>
+      </c>
+      <c r="Z169">
+        <v>1</v>
+      </c>
+      <c r="AA169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:27">
       <c r="A170" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="B170" s="1"/>
       <c r="C170">
         <v>1</v>
       </c>
+      <c r="D170">
+        <v>1</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170">
+        <v>1</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
       <c r="J170">
         <v>1</v>
       </c>
@@ -13854,17 +14763,69 @@
       <c r="O170">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:21">
+      <c r="P170">
+        <v>1</v>
+      </c>
+      <c r="Q170">
+        <v>1</v>
+      </c>
+      <c r="R170">
+        <v>1</v>
+      </c>
+      <c r="S170">
+        <v>1</v>
+      </c>
+      <c r="T170">
+        <v>1</v>
+      </c>
+      <c r="U170">
+        <v>1</v>
+      </c>
+      <c r="V170">
+        <v>1</v>
+      </c>
+      <c r="W170">
+        <v>1</v>
+      </c>
+      <c r="X170">
+        <v>1</v>
+      </c>
+      <c r="Y170">
+        <v>1</v>
+      </c>
+      <c r="Z170">
+        <v>1</v>
+      </c>
+      <c r="AA170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:27">
       <c r="A171" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="B171" s="1"/>
       <c r="C171">
         <v>1</v>
       </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+      <c r="E171">
+        <v>1</v>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+      <c r="H171">
+        <v>1</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
       <c r="J171">
         <v>1</v>
       </c>
@@ -13883,17 +14844,69 @@
       <c r="O171">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" spans="1:21">
+      <c r="P171">
+        <v>1</v>
+      </c>
+      <c r="Q171">
+        <v>1</v>
+      </c>
+      <c r="R171">
+        <v>1</v>
+      </c>
+      <c r="S171">
+        <v>1</v>
+      </c>
+      <c r="T171">
+        <v>1</v>
+      </c>
+      <c r="U171">
+        <v>1</v>
+      </c>
+      <c r="V171">
+        <v>1</v>
+      </c>
+      <c r="W171">
+        <v>1</v>
+      </c>
+      <c r="X171">
+        <v>1</v>
+      </c>
+      <c r="Y171">
+        <v>1</v>
+      </c>
+      <c r="Z171">
+        <v>1</v>
+      </c>
+      <c r="AA171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:27">
       <c r="A172" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="B172" s="1"/>
       <c r="C172">
         <v>1</v>
       </c>
+      <c r="D172">
+        <v>1</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+      <c r="F172">
+        <v>1</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172">
+        <v>1</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
       <c r="J172">
         <v>1</v>
       </c>
@@ -13912,17 +14925,87 @@
       <c r="O172">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:21">
+      <c r="P172">
+        <v>1</v>
+      </c>
+      <c r="Q172">
+        <v>1</v>
+      </c>
+      <c r="R172">
+        <v>1</v>
+      </c>
+      <c r="S172">
+        <v>1</v>
+      </c>
+      <c r="T172">
+        <v>1</v>
+      </c>
+      <c r="U172">
+        <v>1</v>
+      </c>
+      <c r="V172">
+        <v>1</v>
+      </c>
+      <c r="W172">
+        <v>1</v>
+      </c>
+      <c r="X172">
+        <v>1</v>
+      </c>
+      <c r="Y172">
+        <v>1</v>
+      </c>
+      <c r="Z172">
+        <v>1</v>
+      </c>
+      <c r="AA172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:27">
       <c r="A173" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>13</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="B173" s="1"/>
       <c r="C173">
         <v>1</v>
       </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+      <c r="E173">
+        <v>1</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173">
+        <v>1</v>
+      </c>
+      <c r="I173">
+        <v>1</v>
+      </c>
+      <c r="J173">
+        <v>1</v>
+      </c>
+      <c r="K173">
+        <v>1</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="M173">
+        <v>1</v>
+      </c>
+      <c r="N173">
+        <v>1</v>
+      </c>
+      <c r="O173">
+        <v>1</v>
+      </c>
       <c r="P173">
         <v>1</v>
       </c>
@@ -13941,17 +15024,69 @@
       <c r="U173">
         <v>1</v>
       </c>
-    </row>
-    <row r="174" spans="1:21">
+      <c r="V173">
+        <v>1</v>
+      </c>
+      <c r="W173">
+        <v>1</v>
+      </c>
+      <c r="X173">
+        <v>1</v>
+      </c>
+      <c r="Y173">
+        <v>1</v>
+      </c>
+      <c r="Z173">
+        <v>1</v>
+      </c>
+      <c r="AA173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:27">
       <c r="A174" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="B174" s="1"/>
       <c r="C174">
         <v>1</v>
       </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
+      <c r="G174">
+        <v>1</v>
+      </c>
+      <c r="H174">
+        <v>1</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>1</v>
+      </c>
+      <c r="M174">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>1</v>
+      </c>
+      <c r="O174">
+        <v>1</v>
+      </c>
       <c r="P174">
         <v>1</v>
       </c>
@@ -13970,17 +15105,69 @@
       <c r="U174">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:21">
+      <c r="V174">
+        <v>1</v>
+      </c>
+      <c r="W174">
+        <v>1</v>
+      </c>
+      <c r="X174">
+        <v>1</v>
+      </c>
+      <c r="Y174">
+        <v>1</v>
+      </c>
+      <c r="Z174">
+        <v>1</v>
+      </c>
+      <c r="AA174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:27">
       <c r="A175" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="B175" s="1"/>
       <c r="C175">
         <v>1</v>
       </c>
+      <c r="D175">
+        <v>1</v>
+      </c>
+      <c r="E175">
+        <v>1</v>
+      </c>
+      <c r="F175">
+        <v>1</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+      <c r="H175">
+        <v>1</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="M175">
+        <v>1</v>
+      </c>
+      <c r="N175">
+        <v>1</v>
+      </c>
+      <c r="O175">
+        <v>1</v>
+      </c>
       <c r="P175">
         <v>1</v>
       </c>
@@ -13999,17 +15186,69 @@
       <c r="U175">
         <v>1</v>
       </c>
-    </row>
-    <row r="176" spans="1:21">
+      <c r="V175">
+        <v>1</v>
+      </c>
+      <c r="W175">
+        <v>1</v>
+      </c>
+      <c r="X175">
+        <v>1</v>
+      </c>
+      <c r="Y175">
+        <v>1</v>
+      </c>
+      <c r="Z175">
+        <v>1</v>
+      </c>
+      <c r="AA175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:27">
       <c r="A176" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="B176" s="1"/>
       <c r="C176">
         <v>1</v>
       </c>
+      <c r="D176">
+        <v>1</v>
+      </c>
+      <c r="E176">
+        <v>1</v>
+      </c>
+      <c r="F176">
+        <v>1</v>
+      </c>
+      <c r="G176">
+        <v>1</v>
+      </c>
+      <c r="H176">
+        <v>1</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176">
+        <v>1</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>1</v>
+      </c>
+      <c r="N176">
+        <v>1</v>
+      </c>
+      <c r="O176">
+        <v>1</v>
+      </c>
       <c r="P176">
         <v>1</v>
       </c>
@@ -14026,19 +15265,71 @@
         <v>1</v>
       </c>
       <c r="U176">
+        <v>1</v>
+      </c>
+      <c r="V176">
+        <v>1</v>
+      </c>
+      <c r="W176">
+        <v>1</v>
+      </c>
+      <c r="X176">
+        <v>1</v>
+      </c>
+      <c r="Y176">
+        <v>1</v>
+      </c>
+      <c r="Z176">
+        <v>1</v>
+      </c>
+      <c r="AA176">
         <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:27">
       <c r="A177" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="B177" s="1"/>
       <c r="C177">
         <v>1</v>
       </c>
+      <c r="D177">
+        <v>1</v>
+      </c>
+      <c r="E177">
+        <v>1</v>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177">
+        <v>1</v>
+      </c>
+      <c r="H177">
+        <v>1</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177">
+        <v>1</v>
+      </c>
+      <c r="M177">
+        <v>1</v>
+      </c>
+      <c r="N177">
+        <v>1</v>
+      </c>
+      <c r="O177">
+        <v>1</v>
+      </c>
       <c r="P177">
         <v>1</v>
       </c>
@@ -14055,19 +15346,71 @@
         <v>1</v>
       </c>
       <c r="U177">
+        <v>1</v>
+      </c>
+      <c r="V177">
+        <v>1</v>
+      </c>
+      <c r="W177">
+        <v>1</v>
+      </c>
+      <c r="X177">
+        <v>1</v>
+      </c>
+      <c r="Y177">
+        <v>1</v>
+      </c>
+      <c r="Z177">
+        <v>1</v>
+      </c>
+      <c r="AA177">
         <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:27">
       <c r="A178" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="B178" s="1"/>
       <c r="C178">
         <v>1</v>
       </c>
+      <c r="D178">
+        <v>1</v>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
+      <c r="F178">
+        <v>1</v>
+      </c>
+      <c r="G178">
+        <v>1</v>
+      </c>
+      <c r="H178">
+        <v>1</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178">
+        <v>1</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178">
+        <v>1</v>
+      </c>
+      <c r="M178">
+        <v>1</v>
+      </c>
+      <c r="N178">
+        <v>1</v>
+      </c>
+      <c r="O178">
+        <v>1</v>
+      </c>
       <c r="P178">
         <v>1</v>
       </c>
@@ -14084,17 +15427,87 @@
         <v>1</v>
       </c>
       <c r="U178">
+        <v>1</v>
+      </c>
+      <c r="V178">
+        <v>1</v>
+      </c>
+      <c r="W178">
+        <v>1</v>
+      </c>
+      <c r="X178">
+        <v>1</v>
+      </c>
+      <c r="Y178">
+        <v>1</v>
+      </c>
+      <c r="Z178">
+        <v>1</v>
+      </c>
+      <c r="AA178">
         <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:27">
       <c r="A179" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="B179" s="1"/>
       <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+      <c r="G179">
+        <v>1</v>
+      </c>
+      <c r="H179">
+        <v>1</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+      <c r="J179">
+        <v>1</v>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <v>1</v>
+      </c>
+      <c r="N179">
+        <v>1</v>
+      </c>
+      <c r="O179">
+        <v>1</v>
+      </c>
+      <c r="P179">
+        <v>1</v>
+      </c>
+      <c r="Q179">
+        <v>1</v>
+      </c>
+      <c r="R179">
+        <v>1</v>
+      </c>
+      <c r="S179">
+        <v>1</v>
+      </c>
+      <c r="T179">
+        <v>1</v>
+      </c>
+      <c r="U179">
         <v>1</v>
       </c>
       <c r="V179">
@@ -14118,12 +15531,64 @@
     </row>
     <row r="180" spans="1:27">
       <c r="A180" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="B180" s="1"/>
       <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180">
+        <v>1</v>
+      </c>
+      <c r="E180">
+        <v>1</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180">
+        <v>1</v>
+      </c>
+      <c r="H180">
+        <v>1</v>
+      </c>
+      <c r="I180">
+        <v>1</v>
+      </c>
+      <c r="J180">
+        <v>1</v>
+      </c>
+      <c r="K180">
+        <v>1</v>
+      </c>
+      <c r="L180">
+        <v>1</v>
+      </c>
+      <c r="M180">
+        <v>1</v>
+      </c>
+      <c r="N180">
+        <v>1</v>
+      </c>
+      <c r="O180">
+        <v>1</v>
+      </c>
+      <c r="P180">
+        <v>1</v>
+      </c>
+      <c r="Q180">
+        <v>1</v>
+      </c>
+      <c r="R180">
+        <v>1</v>
+      </c>
+      <c r="S180">
+        <v>1</v>
+      </c>
+      <c r="T180">
+        <v>1</v>
+      </c>
+      <c r="U180">
         <v>1</v>
       </c>
       <c r="V180">
@@ -14147,12 +15612,64 @@
     </row>
     <row r="181" spans="1:27">
       <c r="A181" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="B181" s="1"/>
       <c r="C181">
+        <v>1</v>
+      </c>
+      <c r="D181">
+        <v>1</v>
+      </c>
+      <c r="E181">
+        <v>1</v>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181">
+        <v>1</v>
+      </c>
+      <c r="H181">
+        <v>1</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181">
+        <v>1</v>
+      </c>
+      <c r="K181">
+        <v>1</v>
+      </c>
+      <c r="L181">
+        <v>1</v>
+      </c>
+      <c r="M181">
+        <v>1</v>
+      </c>
+      <c r="N181">
+        <v>1</v>
+      </c>
+      <c r="O181">
+        <v>1</v>
+      </c>
+      <c r="P181">
+        <v>1</v>
+      </c>
+      <c r="Q181">
+        <v>1</v>
+      </c>
+      <c r="R181">
+        <v>1</v>
+      </c>
+      <c r="S181">
+        <v>1</v>
+      </c>
+      <c r="T181">
+        <v>1</v>
+      </c>
+      <c r="U181">
         <v>1</v>
       </c>
       <c r="V181">
@@ -14176,12 +15693,64 @@
     </row>
     <row r="182" spans="1:27">
       <c r="A182" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="B182" s="1"/>
       <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182">
+        <v>1</v>
+      </c>
+      <c r="E182">
+        <v>1</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182">
+        <v>1</v>
+      </c>
+      <c r="H182">
+        <v>1</v>
+      </c>
+      <c r="I182">
+        <v>1</v>
+      </c>
+      <c r="J182">
+        <v>1</v>
+      </c>
+      <c r="K182">
+        <v>1</v>
+      </c>
+      <c r="L182">
+        <v>1</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>1</v>
+      </c>
+      <c r="O182">
+        <v>1</v>
+      </c>
+      <c r="P182">
+        <v>1</v>
+      </c>
+      <c r="Q182">
+        <v>1</v>
+      </c>
+      <c r="R182">
+        <v>1</v>
+      </c>
+      <c r="S182">
+        <v>1</v>
+      </c>
+      <c r="T182">
+        <v>1</v>
+      </c>
+      <c r="U182">
         <v>1</v>
       </c>
       <c r="V182">
@@ -14205,12 +15774,64 @@
     </row>
     <row r="183" spans="1:27">
       <c r="A183" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="B183" s="1"/>
       <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183">
+        <v>1</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183">
+        <v>1</v>
+      </c>
+      <c r="H183">
+        <v>1</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183">
+        <v>1</v>
+      </c>
+      <c r="K183">
+        <v>1</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="M183">
+        <v>1</v>
+      </c>
+      <c r="N183">
+        <v>1</v>
+      </c>
+      <c r="O183">
+        <v>1</v>
+      </c>
+      <c r="P183">
+        <v>1</v>
+      </c>
+      <c r="Q183">
+        <v>1</v>
+      </c>
+      <c r="R183">
+        <v>1</v>
+      </c>
+      <c r="S183">
+        <v>1</v>
+      </c>
+      <c r="T183">
+        <v>1</v>
+      </c>
+      <c r="U183">
         <v>1</v>
       </c>
       <c r="V183">
@@ -14234,12 +15855,64 @@
     </row>
     <row r="184" spans="1:27">
       <c r="A184" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="B184" s="1"/>
       <c r="C184">
+        <v>1</v>
+      </c>
+      <c r="D184">
+        <v>1</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184">
+        <v>1</v>
+      </c>
+      <c r="H184">
+        <v>1</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="J184">
+        <v>1</v>
+      </c>
+      <c r="K184">
+        <v>1</v>
+      </c>
+      <c r="L184">
+        <v>1</v>
+      </c>
+      <c r="M184">
+        <v>1</v>
+      </c>
+      <c r="N184">
+        <v>1</v>
+      </c>
+      <c r="O184">
+        <v>1</v>
+      </c>
+      <c r="P184">
+        <v>1</v>
+      </c>
+      <c r="Q184">
+        <v>1</v>
+      </c>
+      <c r="R184">
+        <v>1</v>
+      </c>
+      <c r="S184">
+        <v>1</v>
+      </c>
+      <c r="T184">
+        <v>1</v>
+      </c>
+      <c r="U184">
         <v>1</v>
       </c>
       <c r="V184">
@@ -14263,105 +15936,443 @@
     </row>
     <row r="185" spans="1:27">
       <c r="A185" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>1</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="B185" s="1"/>
       <c r="C185">
         <v>1</v>
       </c>
+      <c r="D185">
+        <v>1</v>
+      </c>
       <c r="E185">
+        <v>1</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185">
+        <v>1</v>
+      </c>
+      <c r="H185">
+        <v>1</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185">
+        <v>1</v>
+      </c>
+      <c r="M185">
+        <v>1</v>
+      </c>
+      <c r="N185">
+        <v>1</v>
+      </c>
+      <c r="O185">
+        <v>1</v>
+      </c>
+      <c r="P185">
+        <v>1</v>
+      </c>
+      <c r="Q185">
+        <v>1</v>
+      </c>
+      <c r="R185">
+        <v>1</v>
+      </c>
+      <c r="S185">
+        <v>1</v>
+      </c>
+      <c r="T185">
+        <v>1</v>
+      </c>
+      <c r="U185">
+        <v>1</v>
+      </c>
+      <c r="V185">
+        <v>1</v>
+      </c>
+      <c r="W185">
+        <v>1</v>
+      </c>
+      <c r="X185">
+        <v>1</v>
+      </c>
+      <c r="Y185">
+        <v>1</v>
+      </c>
+      <c r="Z185">
+        <v>1</v>
+      </c>
+      <c r="AA185">
         <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:27">
       <c r="A186" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="B186" s="1"/>
       <c r="C186">
         <v>1</v>
       </c>
+      <c r="D186">
+        <v>1</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
       <c r="F186">
+        <v>1</v>
+      </c>
+      <c r="G186">
+        <v>1</v>
+      </c>
+      <c r="H186">
+        <v>1</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>1</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
+      </c>
+      <c r="M186">
+        <v>1</v>
+      </c>
+      <c r="N186">
+        <v>1</v>
+      </c>
+      <c r="O186">
+        <v>1</v>
+      </c>
+      <c r="P186">
+        <v>1</v>
+      </c>
+      <c r="Q186">
+        <v>1</v>
+      </c>
+      <c r="R186">
+        <v>1</v>
+      </c>
+      <c r="S186">
+        <v>1</v>
+      </c>
+      <c r="T186">
+        <v>1</v>
+      </c>
+      <c r="U186">
+        <v>1</v>
+      </c>
+      <c r="V186">
+        <v>1</v>
+      </c>
+      <c r="W186">
+        <v>1</v>
+      </c>
+      <c r="X186">
+        <v>1</v>
+      </c>
+      <c r="Y186">
+        <v>1</v>
+      </c>
+      <c r="Z186">
+        <v>1</v>
+      </c>
+      <c r="AA186">
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:27">
       <c r="A187" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="B187" s="1"/>
       <c r="C187">
         <v>1</v>
       </c>
+      <c r="D187">
+        <v>1</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187">
+        <v>1</v>
+      </c>
       <c r="H187">
+        <v>1</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="J187">
+        <v>1</v>
+      </c>
+      <c r="K187">
+        <v>1</v>
+      </c>
+      <c r="L187">
+        <v>1</v>
+      </c>
+      <c r="M187">
+        <v>1</v>
+      </c>
+      <c r="N187">
+        <v>1</v>
+      </c>
+      <c r="O187">
+        <v>1</v>
+      </c>
+      <c r="P187">
+        <v>1</v>
+      </c>
+      <c r="Q187">
+        <v>1</v>
+      </c>
+      <c r="R187">
+        <v>1</v>
+      </c>
+      <c r="S187">
+        <v>1</v>
+      </c>
+      <c r="T187">
+        <v>1</v>
+      </c>
+      <c r="U187">
+        <v>1</v>
+      </c>
+      <c r="V187">
+        <v>1</v>
+      </c>
+      <c r="W187">
+        <v>1</v>
+      </c>
+      <c r="X187">
+        <v>1</v>
+      </c>
+      <c r="Y187">
+        <v>1</v>
+      </c>
+      <c r="Z187">
+        <v>1</v>
+      </c>
+      <c r="AA187">
         <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:27">
       <c r="A188" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="B188" s="1"/>
       <c r="C188">
         <v>1</v>
       </c>
+      <c r="D188">
+        <v>1</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+      <c r="G188">
+        <v>1</v>
+      </c>
+      <c r="H188">
+        <v>1</v>
+      </c>
       <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="J188">
+        <v>1</v>
+      </c>
+      <c r="K188">
+        <v>1</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="M188">
+        <v>1</v>
+      </c>
+      <c r="N188">
+        <v>1</v>
+      </c>
+      <c r="O188">
+        <v>1</v>
+      </c>
+      <c r="P188">
+        <v>1</v>
+      </c>
+      <c r="Q188">
+        <v>1</v>
+      </c>
+      <c r="R188">
+        <v>1</v>
+      </c>
+      <c r="S188">
+        <v>1</v>
+      </c>
+      <c r="T188">
+        <v>1</v>
+      </c>
+      <c r="U188">
+        <v>1</v>
+      </c>
+      <c r="V188">
+        <v>1</v>
+      </c>
+      <c r="W188">
+        <v>1</v>
+      </c>
+      <c r="X188">
+        <v>1</v>
+      </c>
+      <c r="Y188">
+        <v>1</v>
+      </c>
+      <c r="Z188">
+        <v>1</v>
+      </c>
+      <c r="AA188">
         <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:27">
       <c r="A189" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="B189" s="1"/>
       <c r="C189">
         <v>1</v>
       </c>
+      <c r="D189">
+        <v>1</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189">
+        <v>1</v>
+      </c>
+      <c r="H189">
+        <v>1</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
       <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="M189">
+        <v>1</v>
+      </c>
+      <c r="N189">
+        <v>1</v>
+      </c>
+      <c r="O189">
+        <v>1</v>
+      </c>
+      <c r="P189">
+        <v>1</v>
+      </c>
+      <c r="Q189">
+        <v>1</v>
+      </c>
+      <c r="R189">
+        <v>1</v>
+      </c>
+      <c r="S189">
+        <v>1</v>
+      </c>
+      <c r="T189">
+        <v>1</v>
+      </c>
+      <c r="U189">
+        <v>1</v>
+      </c>
+      <c r="V189">
+        <v>1</v>
+      </c>
+      <c r="W189">
+        <v>1</v>
+      </c>
+      <c r="X189">
+        <v>1</v>
+      </c>
+      <c r="Y189">
+        <v>1</v>
+      </c>
+      <c r="Z189">
+        <v>1</v>
+      </c>
+      <c r="AA189">
         <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:27">
       <c r="A190" s="1" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C190">
         <v>1</v>
       </c>
-      <c r="L190">
+      <c r="D190">
         <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:27">
       <c r="A191" s="1" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
-      <c r="N191">
+      <c r="D191">
+        <v>1</v>
+      </c>
+      <c r="G191">
         <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:27">
       <c r="A192" s="1" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>11</v>
@@ -14369,119 +16380,964 @@
       <c r="C192">
         <v>1</v>
       </c>
-      <c r="O192">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:27">
+      <c r="J192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:21">
       <c r="A193" s="1" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="B193" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C193">
+        <v>1</v>
+      </c>
+      <c r="J193">
+        <v>1</v>
+      </c>
+      <c r="M193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:21">
+      <c r="A194" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="M194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:21">
+      <c r="A195" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C195">
+        <v>1</v>
+      </c>
+      <c r="D195">
+        <v>1</v>
+      </c>
+      <c r="E195">
+        <v>1</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+      <c r="G195">
+        <v>1</v>
+      </c>
+      <c r="H195">
+        <v>1</v>
+      </c>
+      <c r="I195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:21">
+      <c r="A196" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+      <c r="D196">
+        <v>1</v>
+      </c>
+      <c r="E196">
+        <v>1</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+      <c r="G196">
+        <v>1</v>
+      </c>
+      <c r="H196">
+        <v>1</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:21">
+      <c r="A197" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197">
+        <v>1</v>
+      </c>
+      <c r="E197">
+        <v>1</v>
+      </c>
+      <c r="F197">
+        <v>1</v>
+      </c>
+      <c r="G197">
+        <v>1</v>
+      </c>
+      <c r="H197">
+        <v>1</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:21">
+      <c r="A198" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C198">
+        <v>1</v>
+      </c>
+      <c r="D198">
+        <v>1</v>
+      </c>
+      <c r="E198">
+        <v>1</v>
+      </c>
+      <c r="F198">
+        <v>1</v>
+      </c>
+      <c r="G198">
+        <v>1</v>
+      </c>
+      <c r="H198">
+        <v>1</v>
+      </c>
+      <c r="I198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:21">
+      <c r="A199" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+      <c r="D199">
+        <v>1</v>
+      </c>
+      <c r="E199">
+        <v>1</v>
+      </c>
+      <c r="F199">
+        <v>1</v>
+      </c>
+      <c r="G199">
+        <v>1</v>
+      </c>
+      <c r="H199">
+        <v>1</v>
+      </c>
+      <c r="I199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:21">
+      <c r="A200" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C200">
+        <v>1</v>
+      </c>
+      <c r="D200">
+        <v>1</v>
+      </c>
+      <c r="E200">
+        <v>1</v>
+      </c>
+      <c r="F200">
+        <v>1</v>
+      </c>
+      <c r="G200">
+        <v>1</v>
+      </c>
+      <c r="H200">
+        <v>1</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:21">
+      <c r="A201" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C201">
+        <v>1</v>
+      </c>
+      <c r="J201">
+        <v>1</v>
+      </c>
+      <c r="K201">
+        <v>1</v>
+      </c>
+      <c r="L201">
+        <v>1</v>
+      </c>
+      <c r="M201">
+        <v>1</v>
+      </c>
+      <c r="N201">
+        <v>1</v>
+      </c>
+      <c r="O201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:21">
+      <c r="A202" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C202">
+        <v>1</v>
+      </c>
+      <c r="J202">
+        <v>1</v>
+      </c>
+      <c r="K202">
+        <v>1</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202">
+        <v>1</v>
+      </c>
+      <c r="N202">
+        <v>1</v>
+      </c>
+      <c r="O202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:21">
+      <c r="A203" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C203">
+        <v>1</v>
+      </c>
+      <c r="J203">
+        <v>1</v>
+      </c>
+      <c r="K203">
+        <v>1</v>
+      </c>
+      <c r="L203">
+        <v>1</v>
+      </c>
+      <c r="M203">
+        <v>1</v>
+      </c>
+      <c r="N203">
+        <v>1</v>
+      </c>
+      <c r="O203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:21">
+      <c r="A204" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C204">
+        <v>1</v>
+      </c>
+      <c r="J204">
+        <v>1</v>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>1</v>
+      </c>
+      <c r="O204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:21">
+      <c r="A205" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205">
+        <v>1</v>
+      </c>
+      <c r="J205">
+        <v>1</v>
+      </c>
+      <c r="K205">
+        <v>1</v>
+      </c>
+      <c r="L205">
+        <v>1</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>1</v>
+      </c>
+      <c r="O205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:21">
+      <c r="A206" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C206">
+        <v>1</v>
+      </c>
+      <c r="J206">
+        <v>1</v>
+      </c>
+      <c r="K206">
+        <v>1</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="M206">
+        <v>1</v>
+      </c>
+      <c r="N206">
+        <v>1</v>
+      </c>
+      <c r="O206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:21">
+      <c r="A207" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C193">
-        <v>1</v>
-      </c>
-      <c r="Q193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:27">
-      <c r="A194" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B194" s="1" t="s">
+      <c r="C207">
+        <v>1</v>
+      </c>
+      <c r="P207">
+        <v>1</v>
+      </c>
+      <c r="Q207">
+        <v>1</v>
+      </c>
+      <c r="R207">
+        <v>1</v>
+      </c>
+      <c r="S207">
+        <v>1</v>
+      </c>
+      <c r="T207">
+        <v>1</v>
+      </c>
+      <c r="U207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:21">
+      <c r="A208" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C194">
-        <v>1</v>
-      </c>
-      <c r="R194">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:27">
-      <c r="A195" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B195" s="1" t="s">
+      <c r="C208">
+        <v>1</v>
+      </c>
+      <c r="P208">
+        <v>1</v>
+      </c>
+      <c r="Q208">
+        <v>1</v>
+      </c>
+      <c r="R208">
+        <v>1</v>
+      </c>
+      <c r="S208">
+        <v>1</v>
+      </c>
+      <c r="T208">
+        <v>1</v>
+      </c>
+      <c r="U208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:27">
+      <c r="A209" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="P209">
+        <v>1</v>
+      </c>
+      <c r="Q209">
+        <v>1</v>
+      </c>
+      <c r="R209">
+        <v>1</v>
+      </c>
+      <c r="S209">
+        <v>1</v>
+      </c>
+      <c r="T209">
+        <v>1</v>
+      </c>
+      <c r="U209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:27">
+      <c r="A210" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C195">
-        <v>1</v>
-      </c>
-      <c r="T195">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:27">
-      <c r="A196" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B196" s="1" t="s">
+      <c r="C210">
+        <v>1</v>
+      </c>
+      <c r="P210">
+        <v>1</v>
+      </c>
+      <c r="Q210">
+        <v>1</v>
+      </c>
+      <c r="R210">
+        <v>1</v>
+      </c>
+      <c r="S210">
+        <v>1</v>
+      </c>
+      <c r="T210">
+        <v>1</v>
+      </c>
+      <c r="U210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:27">
+      <c r="A211" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C196">
-        <v>1</v>
-      </c>
-      <c r="U196">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197" spans="1:27">
-      <c r="A197" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B197" s="1" t="s">
+      <c r="C211">
+        <v>1</v>
+      </c>
+      <c r="P211">
+        <v>1</v>
+      </c>
+      <c r="Q211">
+        <v>1</v>
+      </c>
+      <c r="R211">
+        <v>1</v>
+      </c>
+      <c r="S211">
+        <v>1</v>
+      </c>
+      <c r="T211">
+        <v>1</v>
+      </c>
+      <c r="U211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:27">
+      <c r="A212" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="P212">
+        <v>1</v>
+      </c>
+      <c r="Q212">
+        <v>1</v>
+      </c>
+      <c r="R212">
+        <v>1</v>
+      </c>
+      <c r="S212">
+        <v>1</v>
+      </c>
+      <c r="T212">
+        <v>1</v>
+      </c>
+      <c r="U212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:27">
+      <c r="A213" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C197">
-        <v>1</v>
-      </c>
-      <c r="W197">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:27">
-      <c r="A198" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B198" s="1" t="s">
+      <c r="C213">
+        <v>1</v>
+      </c>
+      <c r="V213">
+        <v>1</v>
+      </c>
+      <c r="W213">
+        <v>1</v>
+      </c>
+      <c r="X213">
+        <v>1</v>
+      </c>
+      <c r="Y213">
+        <v>1</v>
+      </c>
+      <c r="Z213">
+        <v>1</v>
+      </c>
+      <c r="AA213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:27">
+      <c r="A214" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C198">
-        <v>1</v>
-      </c>
-      <c r="X198">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:27">
-      <c r="A199" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B199" s="1" t="s">
+      <c r="C214">
+        <v>1</v>
+      </c>
+      <c r="V214">
+        <v>1</v>
+      </c>
+      <c r="W214">
+        <v>1</v>
+      </c>
+      <c r="X214">
+        <v>1</v>
+      </c>
+      <c r="Y214">
+        <v>1</v>
+      </c>
+      <c r="Z214">
+        <v>1</v>
+      </c>
+      <c r="AA214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:27">
+      <c r="A215" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="V215">
+        <v>1</v>
+      </c>
+      <c r="W215">
+        <v>1</v>
+      </c>
+      <c r="X215">
+        <v>1</v>
+      </c>
+      <c r="Y215">
+        <v>1</v>
+      </c>
+      <c r="Z215">
+        <v>1</v>
+      </c>
+      <c r="AA215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:27">
+      <c r="A216" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C199">
-        <v>1</v>
-      </c>
-      <c r="Z199">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:27">
-      <c r="A200" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B200" s="1" t="s">
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="V216">
+        <v>1</v>
+      </c>
+      <c r="W216">
+        <v>1</v>
+      </c>
+      <c r="X216">
+        <v>1</v>
+      </c>
+      <c r="Y216">
+        <v>1</v>
+      </c>
+      <c r="Z216">
+        <v>1</v>
+      </c>
+      <c r="AA216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:27">
+      <c r="A217" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C200">
-        <v>1</v>
-      </c>
-      <c r="AA200">
+      <c r="C217">
+        <v>1</v>
+      </c>
+      <c r="V217">
+        <v>1</v>
+      </c>
+      <c r="W217">
+        <v>1</v>
+      </c>
+      <c r="X217">
+        <v>1</v>
+      </c>
+      <c r="Y217">
+        <v>1</v>
+      </c>
+      <c r="Z217">
+        <v>1</v>
+      </c>
+      <c r="AA217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:27">
+      <c r="A218" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+      <c r="V218">
+        <v>1</v>
+      </c>
+      <c r="W218">
+        <v>1</v>
+      </c>
+      <c r="X218">
+        <v>1</v>
+      </c>
+      <c r="Y218">
+        <v>1</v>
+      </c>
+      <c r="Z218">
+        <v>1</v>
+      </c>
+      <c r="AA218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:27">
+      <c r="A219" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
+      <c r="E219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:27">
+      <c r="A220" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+      <c r="F220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:27">
+      <c r="A221" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+      <c r="H221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:27">
+      <c r="A222" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+      <c r="I222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:27">
+      <c r="A223" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:27">
+      <c r="A224" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+      <c r="L224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:27">
+      <c r="A225" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C225">
+        <v>1</v>
+      </c>
+      <c r="N225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:27">
+      <c r="A226" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
+      </c>
+      <c r="O226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:27">
+      <c r="A227" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C227">
+        <v>1</v>
+      </c>
+      <c r="Q227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:27">
+      <c r="A228" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="R228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:27">
+      <c r="A229" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C229">
+        <v>1</v>
+      </c>
+      <c r="T229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:27">
+      <c r="A230" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C230">
+        <v>1</v>
+      </c>
+      <c r="U230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:27">
+      <c r="A231" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C231">
+        <v>1</v>
+      </c>
+      <c r="W231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:27">
+      <c r="A232" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+      <c r="X232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:27">
+      <c r="A233" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+      <c r="Z233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:27">
+      <c r="A234" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+      <c r="AA234">
         <v>1</v>
       </c>
     </row>

--- a/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
+++ b/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
@@ -2680,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>2.390869140625</v>
       </c>
       <c r="L21">
         <v>1</v>
@@ -2689,46 +2689,46 @@
         <v>1</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>2.778805923461914</v>
       </c>
       <c r="O21">
         <v>1</v>
       </c>
       <c r="P21">
-        <v>1</v>
+        <v>0.6186035156250002</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>1.3625</v>
       </c>
       <c r="R21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>0.5039062499999999</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <v>1.39853515625</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>0.8529663085937498</v>
       </c>
       <c r="V21">
-        <v>1</v>
+        <v>0.5636718749999999</v>
       </c>
       <c r="W21">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1</v>
+        <v>0.553125</v>
       </c>
       <c r="Z21">
-        <v>1</v>
+        <v>1.1734375</v>
       </c>
       <c r="AA21">
-        <v>1</v>
+        <v>0.1366455078124999</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -3469,76 +3469,76 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>0.01</v>
+        <v>1.74951171875</v>
       </c>
       <c r="F31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="G31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="H31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="I31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>0.01</v>
+        <v>0.4225950754582883</v>
       </c>
       <c r="L31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="N31">
-        <v>0.01</v>
+        <v>0.7672296648796512</v>
       </c>
       <c r="O31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>0.01</v>
+        <v>1.274767804536968</v>
       </c>
       <c r="Q31">
-        <v>0.01</v>
+        <v>0.7889067854897236</v>
       </c>
       <c r="R31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="S31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="T31">
-        <v>0.01</v>
+        <v>0.840020327673646</v>
       </c>
       <c r="U31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>0.01</v>
+        <v>0.1409944878960028</v>
       </c>
       <c r="W31">
-        <v>0.01</v>
+        <v>0.4837021567493677</v>
       </c>
       <c r="X31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="Y31">
-        <v>0.01</v>
+        <v>0.1409252020835876</v>
       </c>
       <c r="Z31">
-        <v>0.01</v>
+        <v>0.4429196078232489</v>
       </c>
       <c r="AA31">
-        <v>0.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -4684,40 +4684,40 @@
         <v>1</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P46">
         <v>1</v>
@@ -4762,79 +4762,79 @@
       </c>
       <c r="B47" s="1"/>
       <c r="C47">
-        <v>1</v>
+        <v>0.5473632812499999</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
-        <v>1.19447265625</v>
+        <v>1</v>
       </c>
       <c r="M47">
         <v>0</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47">
-        <v>0.7985742187499999</v>
+        <v>1</v>
       </c>
       <c r="P47">
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47">
-        <v>0.1823400297619048</v>
+        <v>1</v>
       </c>
       <c r="S47">
         <v>0</v>
       </c>
       <c r="T47">
-        <v>0.24345703125</v>
+        <v>1</v>
       </c>
       <c r="U47">
-        <v>0.4051450117807538</v>
+        <v>1</v>
       </c>
       <c r="V47">
         <v>0</v>
       </c>
       <c r="W47">
-        <v>0.4725</v>
+        <v>1</v>
       </c>
       <c r="X47">
-        <v>0.855</v>
+        <v>1</v>
       </c>
       <c r="Y47">
         <v>0</v>
       </c>
       <c r="Z47">
-        <v>0.0525</v>
+        <v>1</v>
       </c>
       <c r="AA47">
-        <v>0.9506249999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4843,79 +4843,79 @@
       </c>
       <c r="B48" s="1"/>
       <c r="C48">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0.5338586425781251</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0.60703125</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0.497900390625</v>
+        <v>1</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48">
         <v>0</v>
       </c>
       <c r="N48">
-        <v>0.5362499999999999</v>
+        <v>1</v>
       </c>
       <c r="O48">
-        <v>0.5012109374999999</v>
+        <v>1</v>
       </c>
       <c r="P48">
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0.1908976135253907</v>
+        <v>1</v>
       </c>
       <c r="R48">
-        <v>1.390847778320313</v>
+        <v>1</v>
       </c>
       <c r="S48">
         <v>0</v>
       </c>
       <c r="T48">
-        <v>0.163740234375</v>
+        <v>1</v>
       </c>
       <c r="U48">
-        <v>0.9250176980909374</v>
+        <v>1</v>
       </c>
       <c r="V48">
         <v>0</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48">
         <v>0</v>
       </c>
       <c r="Z48">
-        <v>0.16875</v>
+        <v>1</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4951,7 +4951,7 @@
         <v>0.05</v>
       </c>
       <c r="L49">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="M49">
         <v>0.05</v>
@@ -4960,19 +4960,19 @@
         <v>0.05</v>
       </c>
       <c r="O49">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>0.05</v>
+        <v>0.04825927734375</v>
       </c>
       <c r="Q49">
         <v>0.05</v>
       </c>
       <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
         <v>0.05</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
       </c>
       <c r="T49">
         <v>0.05</v>
@@ -4981,19 +4981,19 @@
         <v>0.05</v>
       </c>
       <c r="V49">
+        <v>0.004306640625</v>
+      </c>
+      <c r="W49">
         <v>0</v>
-      </c>
-      <c r="W49">
-        <v>0.05</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49">
+        <v>3.906250000000001E-05</v>
+      </c>
+      <c r="Z49">
         <v>0</v>
-      </c>
-      <c r="Z49">
-        <v>0.05</v>
       </c>
       <c r="AA49">
         <v>0</v>
@@ -9061,73 +9061,73 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G100">
         <v>0</v>
       </c>
       <c r="H100">
-        <v>0.6639597089471153</v>
+        <v>0.02188992165435021</v>
       </c>
       <c r="I100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100">
-        <v>2.722714198835427</v>
+        <v>1</v>
       </c>
       <c r="L100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M100">
         <v>0</v>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>0.1818446836715887</v>
       </c>
       <c r="O100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P100">
         <v>0</v>
       </c>
       <c r="Q100">
-        <v>4.231301884319995</v>
+        <v>1</v>
       </c>
       <c r="R100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S100">
         <v>0</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V100">
         <v>0</v>
       </c>
       <c r="W100">
-        <v>0.730078125</v>
+        <v>0.8283929511161988</v>
       </c>
       <c r="X100">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y100">
         <v>0</v>
       </c>
       <c r="Z100">
-        <v>0.309375</v>
+        <v>0.4791445312499999</v>
       </c>
       <c r="AA100">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:27">
@@ -9142,25 +9142,25 @@
         <v>1</v>
       </c>
       <c r="E101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G101">
         <v>1</v>
       </c>
       <c r="H101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J101">
         <v>1</v>
       </c>
       <c r="K101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -9169,46 +9169,46 @@
         <v>1</v>
       </c>
       <c r="N101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P101">
         <v>1</v>
       </c>
       <c r="Q101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S101">
         <v>1</v>
       </c>
       <c r="T101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V101">
         <v>1</v>
       </c>
       <c r="W101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y101">
         <v>1</v>
       </c>
       <c r="Z101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA101">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:27">
@@ -14488,19 +14488,19 @@
         <v>1</v>
       </c>
       <c r="E167">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G167">
         <v>1</v>
       </c>
       <c r="H167">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I167">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J167">
         <v>1</v>

--- a/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
+++ b/calibrations/Y-factors/hbv_hepaus_calibrations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="241">
   <si>
     <t>meta_y_factor</t>
   </si>
@@ -154,6 +154,12 @@
     <t>hep_dth</t>
   </si>
   <si>
+    <t>dc_death</t>
+  </si>
+  <si>
+    <t>hcc_death</t>
+  </si>
+  <si>
     <t>imig_prev</t>
   </si>
   <si>
@@ -328,7 +334,70 @@
     <t>treat_price</t>
   </si>
   <si>
-    <t>stat_year_life</t>
+    <t>annual_salary</t>
+  </si>
+  <si>
+    <t>etp_ratio</t>
+  </si>
+  <si>
+    <t>ypll_1519</t>
+  </si>
+  <si>
+    <t>dp_1519</t>
+  </si>
+  <si>
+    <t>ypll_2024</t>
+  </si>
+  <si>
+    <t>dp_2024</t>
+  </si>
+  <si>
+    <t>ypll_2529</t>
+  </si>
+  <si>
+    <t>dp_2529</t>
+  </si>
+  <si>
+    <t>ypll_3034</t>
+  </si>
+  <si>
+    <t>dp_3034</t>
+  </si>
+  <si>
+    <t>ypll_3539</t>
+  </si>
+  <si>
+    <t>dp_3539</t>
+  </si>
+  <si>
+    <t>ypll_4044</t>
+  </si>
+  <si>
+    <t>dp_4044</t>
+  </si>
+  <si>
+    <t>ypll_4549</t>
+  </si>
+  <si>
+    <t>dp_4549</t>
+  </si>
+  <si>
+    <t>ypll_5054</t>
+  </si>
+  <si>
+    <t>dp_5054</t>
+  </si>
+  <si>
+    <t>ypll_5559</t>
+  </si>
+  <si>
+    <t>dp_5559</t>
+  </si>
+  <si>
+    <t>ypll_6064</t>
+  </si>
+  <si>
+    <t>dp_6064</t>
   </si>
   <si>
     <t>ql_clr</t>
@@ -640,7 +709,7 @@
     <t>direct_costs</t>
   </si>
   <si>
-    <t>mort_cost</t>
+    <t>prod_loss</t>
   </si>
   <si>
     <t>qalys_clr</t>
@@ -1025,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA234"/>
+  <dimension ref="A1:AA257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
@@ -2680,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="K21">
-        <v>2.390869140625</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <v>1</v>
@@ -2689,46 +2758,46 @@
         <v>1</v>
       </c>
       <c r="N21">
-        <v>2.778805923461914</v>
+        <v>1</v>
       </c>
       <c r="O21">
         <v>1</v>
       </c>
       <c r="P21">
-        <v>0.6186035156250002</v>
+        <v>1</v>
       </c>
       <c r="Q21">
-        <v>1.3625</v>
+        <v>1</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21">
-        <v>0.5039062499999999</v>
+        <v>1</v>
       </c>
       <c r="T21">
-        <v>1.39853515625</v>
+        <v>1</v>
       </c>
       <c r="U21">
-        <v>0.8529663085937498</v>
+        <v>1</v>
       </c>
       <c r="V21">
-        <v>0.5636718749999999</v>
+        <v>1</v>
       </c>
       <c r="W21">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0.553125</v>
+        <v>1</v>
       </c>
       <c r="Z21">
-        <v>1.1734375</v>
+        <v>1</v>
       </c>
       <c r="AA21">
-        <v>0.1366455078124999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -2842,7 +2911,7 @@
         <v>1</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>2.390869140625</v>
       </c>
       <c r="L23">
         <v>1</v>
@@ -2851,46 +2920,46 @@
         <v>1</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>2.778805923461914</v>
       </c>
       <c r="O23">
         <v>1</v>
       </c>
       <c r="P23">
-        <v>1</v>
+        <v>0.6186035156250002</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>1.3625</v>
       </c>
       <c r="R23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1</v>
+        <v>0.5039062499999999</v>
       </c>
       <c r="T23">
-        <v>1</v>
+        <v>1.39853515625</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>0.8529663085937498</v>
       </c>
       <c r="V23">
-        <v>1</v>
+        <v>0.5636718749999999</v>
       </c>
       <c r="W23">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1</v>
+        <v>0.553125</v>
       </c>
       <c r="Z23">
-        <v>1</v>
+        <v>1.1734375</v>
       </c>
       <c r="AA23">
-        <v>1</v>
+        <v>0.1366455078124999</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -3469,76 +3538,76 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>1.74951171875</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K31">
-        <v>0.4225950754582883</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N31">
-        <v>0.7672296648796512</v>
+        <v>1</v>
       </c>
       <c r="O31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P31">
-        <v>1.274767804536968</v>
+        <v>1</v>
       </c>
       <c r="Q31">
-        <v>0.7889067854897236</v>
+        <v>1</v>
       </c>
       <c r="R31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T31">
-        <v>0.840020327673646</v>
+        <v>1</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V31">
-        <v>0.1409944878960028</v>
+        <v>1</v>
       </c>
       <c r="W31">
-        <v>0.4837021567493677</v>
+        <v>1</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>0.1409252020835876</v>
+        <v>1</v>
       </c>
       <c r="Z31">
-        <v>0.4429196078232489</v>
+        <v>1</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -3631,76 +3700,76 @@
         <v>1</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>1.74951171875</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>1</v>
+        <v>0.4225950754582883</v>
       </c>
       <c r="L33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>0.7672296648796512</v>
       </c>
       <c r="O33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>1</v>
+        <v>1.274767804536968</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>0.7889067854897236</v>
       </c>
       <c r="R33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>1</v>
+        <v>0.840020327673646</v>
       </c>
       <c r="U33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V33">
-        <v>1</v>
+        <v>0.1409944878960028</v>
       </c>
       <c r="W33">
-        <v>1</v>
+        <v>0.4837021567493677</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
-        <v>1</v>
+        <v>0.1409252020835876</v>
       </c>
       <c r="Z33">
-        <v>1</v>
+        <v>0.4429196078232489</v>
       </c>
       <c r="AA33">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -4684,40 +4753,40 @@
         <v>1</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46">
         <v>1</v>
@@ -4762,10 +4831,10 @@
       </c>
       <c r="B47" s="1"/>
       <c r="C47">
-        <v>0.5473632812499999</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -4774,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -4783,7 +4852,7 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47">
         <v>1</v>
@@ -4792,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47">
         <v>1</v>
@@ -4801,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47">
         <v>1</v>
@@ -4810,7 +4879,7 @@
         <v>1</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47">
         <v>1</v>
@@ -4819,7 +4888,7 @@
         <v>1</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47">
         <v>1</v>
@@ -4828,7 +4897,7 @@
         <v>1</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z47">
         <v>1</v>
@@ -4843,46 +4912,46 @@
       </c>
       <c r="B48" s="1"/>
       <c r="C48">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48">
         <v>0</v>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48">
         <v>1</v>
@@ -4891,7 +4960,7 @@
         <v>1</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48">
         <v>1</v>
@@ -4900,7 +4969,7 @@
         <v>1</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48">
         <v>1</v>
@@ -4909,7 +4978,7 @@
         <v>1</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z48">
         <v>1</v>
@@ -4924,79 +4993,79 @@
       </c>
       <c r="B49" s="1"/>
       <c r="C49">
-        <v>1</v>
+        <v>0.523843765258789</v>
       </c>
       <c r="D49">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>0.05</v>
+        <v>1.39</v>
       </c>
       <c r="F49">
-        <v>0.05</v>
+        <v>7.96</v>
       </c>
       <c r="G49">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>0.05</v>
+        <v>1.46</v>
       </c>
       <c r="I49">
-        <v>0.05</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="J49">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>0.05</v>
+        <v>0.72</v>
       </c>
       <c r="L49">
+        <v>0.9</v>
+      </c>
+      <c r="M49">
         <v>0</v>
       </c>
-      <c r="M49">
-        <v>0.05</v>
-      </c>
       <c r="N49">
-        <v>0.05</v>
+        <v>0.91</v>
       </c>
       <c r="O49">
+        <v>1.14</v>
+      </c>
+      <c r="P49">
         <v>0</v>
       </c>
-      <c r="P49">
-        <v>0.04825927734375</v>
-      </c>
       <c r="Q49">
-        <v>0.05</v>
+        <v>0.67</v>
       </c>
       <c r="R49">
+        <v>1</v>
+      </c>
+      <c r="S49">
         <v>0</v>
       </c>
-      <c r="S49">
-        <v>0.05</v>
-      </c>
       <c r="T49">
-        <v>0.05</v>
+        <v>1.01</v>
       </c>
       <c r="U49">
-        <v>0.05</v>
+        <v>1.31</v>
       </c>
       <c r="V49">
-        <v>0.004306640625</v>
+        <v>0</v>
       </c>
       <c r="W49">
+        <v>0.64</v>
+      </c>
+      <c r="X49">
+        <v>0.84</v>
+      </c>
+      <c r="Y49">
         <v>0</v>
       </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
-        <v>3.906250000000001E-05</v>
-      </c>
       <c r="Z49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -5005,79 +5074,79 @@
       </c>
       <c r="B50" s="1"/>
       <c r="C50">
-        <v>1</v>
+        <v>0.04050113105773926</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>4.22</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>22.57</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2.88</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>7.43</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="O50">
-        <v>1</v>
+        <v>7.04</v>
       </c>
       <c r="P50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R50">
-        <v>1</v>
+        <v>12.05</v>
       </c>
       <c r="S50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="U50">
-        <v>1</v>
+        <v>12.27</v>
       </c>
       <c r="V50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1</v>
+        <v>0.47</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>8.49</v>
       </c>
       <c r="Y50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="AA50">
-        <v>1</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -5089,76 +5158,76 @@
         <v>1</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="K51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="L51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="O51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>1</v>
+        <v>0.04825927734375</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="R51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="T51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="U51">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="V51">
-        <v>1</v>
+        <v>0.004306640625</v>
       </c>
       <c r="W51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>1</v>
+        <v>3.906250000000001E-05</v>
       </c>
       <c r="Z51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -8023,28 +8092,28 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="K87">
         <v>1</v>
       </c>
       <c r="L87">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="M87">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N87">
         <v>1</v>
       </c>
       <c r="O87">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P87">
         <v>1</v>
       </c>
       <c r="Q87">
-        <v>0.9500000000000001</v>
+        <v>1</v>
       </c>
       <c r="R87">
         <v>1</v>
@@ -8053,7 +8122,7 @@
         <v>1</v>
       </c>
       <c r="T87">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U87">
         <v>1</v>
@@ -8062,16 +8131,16 @@
         <v>1</v>
       </c>
       <c r="W87">
-        <v>0.825</v>
+        <v>1</v>
       </c>
       <c r="X87">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Y87">
         <v>1</v>
       </c>
       <c r="Z87">
-        <v>1.15625</v>
+        <v>1</v>
       </c>
       <c r="AA87">
         <v>1</v>
@@ -9058,7 +9127,7 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -9067,16 +9136,16 @@
         <v>1</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100">
-        <v>0.02188992165435021</v>
+        <v>1</v>
       </c>
       <c r="I100">
         <v>1</v>
       </c>
       <c r="J100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100">
         <v>1</v>
@@ -9085,16 +9154,16 @@
         <v>1</v>
       </c>
       <c r="M100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N100">
-        <v>0.1818446836715887</v>
+        <v>1</v>
       </c>
       <c r="O100">
         <v>1</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q100">
         <v>1</v>
@@ -9103,7 +9172,7 @@
         <v>1</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100">
         <v>1</v>
@@ -9112,19 +9181,19 @@
         <v>1</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100">
-        <v>0.8283929511161988</v>
+        <v>1</v>
       </c>
       <c r="X100">
         <v>1</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z100">
-        <v>0.4791445312499999</v>
+        <v>1</v>
       </c>
       <c r="AA100">
         <v>1</v>
@@ -9163,7 +9232,7 @@
         <v>1</v>
       </c>
       <c r="L101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101">
         <v>1</v>
@@ -9886,28 +9955,28 @@
         <v>1</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K110">
         <v>1</v>
       </c>
       <c r="L110">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="M110">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N110">
         <v>1</v>
       </c>
       <c r="O110">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P110">
         <v>1</v>
       </c>
       <c r="Q110">
-        <v>1</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="R110">
         <v>1</v>
@@ -9916,7 +9985,7 @@
         <v>1</v>
       </c>
       <c r="T110">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U110">
         <v>1</v>
@@ -9925,16 +9994,16 @@
         <v>1</v>
       </c>
       <c r="W110">
-        <v>1</v>
+        <v>0.825</v>
       </c>
       <c r="X110">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y110">
         <v>1</v>
       </c>
       <c r="Z110">
-        <v>1</v>
+        <v>1.15625</v>
       </c>
       <c r="AA110">
         <v>1</v>
@@ -10921,7 +10990,7 @@
         <v>1</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -10930,16 +10999,16 @@
         <v>1</v>
       </c>
       <c r="G123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>1</v>
+        <v>0.02188992165435021</v>
       </c>
       <c r="I123">
         <v>1</v>
       </c>
       <c r="J123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K123">
         <v>1</v>
@@ -10948,16 +11017,16 @@
         <v>1</v>
       </c>
       <c r="M123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N123">
-        <v>1</v>
+        <v>0.1818446836715887</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q123">
         <v>1</v>
@@ -10966,7 +11035,7 @@
         <v>1</v>
       </c>
       <c r="S123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T123">
         <v>1</v>
@@ -10975,19 +11044,19 @@
         <v>1</v>
       </c>
       <c r="V123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W123">
-        <v>1</v>
+        <v>0.8283929511161988</v>
       </c>
       <c r="X123">
         <v>1</v>
       </c>
       <c r="Y123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z123">
-        <v>1</v>
+        <v>0.4791445312499999</v>
       </c>
       <c r="AA123">
         <v>1</v>
@@ -11026,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="L124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124">
         <v>1</v>
@@ -14488,19 +14557,19 @@
         <v>1</v>
       </c>
       <c r="E167">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F167">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G167">
         <v>1</v>
       </c>
       <c r="H167">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I167">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J167">
         <v>1</v>
@@ -16343,91 +16412,412 @@
       <c r="A190" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B190" s="1"/>
       <c r="C190">
         <v>1</v>
       </c>
       <c r="D190">
+        <v>1</v>
+      </c>
+      <c r="E190">
+        <v>10</v>
+      </c>
+      <c r="F190">
+        <v>10</v>
+      </c>
+      <c r="G190">
+        <v>1</v>
+      </c>
+      <c r="H190">
+        <v>10</v>
+      </c>
+      <c r="I190">
+        <v>10</v>
+      </c>
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="K190">
+        <v>1</v>
+      </c>
+      <c r="L190">
+        <v>1</v>
+      </c>
+      <c r="M190">
+        <v>1</v>
+      </c>
+      <c r="N190">
+        <v>1</v>
+      </c>
+      <c r="O190">
+        <v>1</v>
+      </c>
+      <c r="P190">
+        <v>1</v>
+      </c>
+      <c r="Q190">
+        <v>1</v>
+      </c>
+      <c r="R190">
+        <v>1</v>
+      </c>
+      <c r="S190">
+        <v>1</v>
+      </c>
+      <c r="T190">
+        <v>1</v>
+      </c>
+      <c r="U190">
+        <v>1</v>
+      </c>
+      <c r="V190">
+        <v>1</v>
+      </c>
+      <c r="W190">
+        <v>1</v>
+      </c>
+      <c r="X190">
+        <v>1</v>
+      </c>
+      <c r="Y190">
+        <v>1</v>
+      </c>
+      <c r="Z190">
+        <v>1</v>
+      </c>
+      <c r="AA190">
         <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:27">
       <c r="A191" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="B191" s="1"/>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191">
         <v>1</v>
       </c>
+      <c r="E191">
+        <v>1</v>
+      </c>
+      <c r="F191">
+        <v>1</v>
+      </c>
       <c r="G191">
+        <v>1</v>
+      </c>
+      <c r="H191">
+        <v>1</v>
+      </c>
+      <c r="I191">
+        <v>1</v>
+      </c>
+      <c r="J191">
+        <v>1</v>
+      </c>
+      <c r="K191">
+        <v>1</v>
+      </c>
+      <c r="L191">
+        <v>1</v>
+      </c>
+      <c r="M191">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>1</v>
+      </c>
+      <c r="O191">
+        <v>1</v>
+      </c>
+      <c r="P191">
+        <v>1</v>
+      </c>
+      <c r="Q191">
+        <v>1</v>
+      </c>
+      <c r="R191">
+        <v>1</v>
+      </c>
+      <c r="S191">
+        <v>1</v>
+      </c>
+      <c r="T191">
+        <v>1</v>
+      </c>
+      <c r="U191">
+        <v>1</v>
+      </c>
+      <c r="V191">
+        <v>1</v>
+      </c>
+      <c r="W191">
+        <v>1</v>
+      </c>
+      <c r="X191">
+        <v>1</v>
+      </c>
+      <c r="Y191">
+        <v>1</v>
+      </c>
+      <c r="Z191">
+        <v>1</v>
+      </c>
+      <c r="AA191">
         <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:27">
       <c r="A192" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="B192" s="1"/>
       <c r="C192">
         <v>1</v>
       </c>
+      <c r="D192">
+        <v>1</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+      <c r="G192">
+        <v>1</v>
+      </c>
+      <c r="H192">
+        <v>1</v>
+      </c>
+      <c r="I192">
+        <v>1</v>
+      </c>
       <c r="J192">
         <v>1</v>
       </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
       <c r="M192">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="1:21">
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192">
+        <v>1</v>
+      </c>
+      <c r="P192">
+        <v>1</v>
+      </c>
+      <c r="Q192">
+        <v>1</v>
+      </c>
+      <c r="R192">
+        <v>1</v>
+      </c>
+      <c r="S192">
+        <v>1</v>
+      </c>
+      <c r="T192">
+        <v>1</v>
+      </c>
+      <c r="U192">
+        <v>1</v>
+      </c>
+      <c r="V192">
+        <v>1</v>
+      </c>
+      <c r="W192">
+        <v>1</v>
+      </c>
+      <c r="X192">
+        <v>1</v>
+      </c>
+      <c r="Y192">
+        <v>1</v>
+      </c>
+      <c r="Z192">
+        <v>1</v>
+      </c>
+      <c r="AA192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:27">
       <c r="A193" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="B193" s="1"/>
       <c r="C193">
         <v>1</v>
       </c>
+      <c r="D193">
+        <v>1</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="G193">
+        <v>1</v>
+      </c>
+      <c r="H193">
+        <v>1</v>
+      </c>
+      <c r="I193">
+        <v>1</v>
+      </c>
       <c r="J193">
         <v>1</v>
       </c>
+      <c r="K193">
+        <v>1</v>
+      </c>
+      <c r="L193">
+        <v>1</v>
+      </c>
       <c r="M193">
         <v>1</v>
       </c>
-    </row>
-    <row r="194" spans="1:21">
+      <c r="N193">
+        <v>1</v>
+      </c>
+      <c r="O193">
+        <v>1</v>
+      </c>
+      <c r="P193">
+        <v>1</v>
+      </c>
+      <c r="Q193">
+        <v>1</v>
+      </c>
+      <c r="R193">
+        <v>1</v>
+      </c>
+      <c r="S193">
+        <v>1</v>
+      </c>
+      <c r="T193">
+        <v>1</v>
+      </c>
+      <c r="U193">
+        <v>1</v>
+      </c>
+      <c r="V193">
+        <v>1</v>
+      </c>
+      <c r="W193">
+        <v>1</v>
+      </c>
+      <c r="X193">
+        <v>1</v>
+      </c>
+      <c r="Y193">
+        <v>1</v>
+      </c>
+      <c r="Z193">
+        <v>1</v>
+      </c>
+      <c r="AA193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:27">
       <c r="A194" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="B194" s="1"/>
       <c r="C194">
         <v>1</v>
       </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194">
+        <v>1</v>
+      </c>
+      <c r="H194">
+        <v>1</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
       <c r="J194">
         <v>1</v>
       </c>
+      <c r="K194">
+        <v>1</v>
+      </c>
+      <c r="L194">
+        <v>1</v>
+      </c>
       <c r="M194">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="1:21">
+      <c r="N194">
+        <v>1</v>
+      </c>
+      <c r="O194">
+        <v>1</v>
+      </c>
+      <c r="P194">
+        <v>1</v>
+      </c>
+      <c r="Q194">
+        <v>1</v>
+      </c>
+      <c r="R194">
+        <v>1</v>
+      </c>
+      <c r="S194">
+        <v>1</v>
+      </c>
+      <c r="T194">
+        <v>1</v>
+      </c>
+      <c r="U194">
+        <v>1</v>
+      </c>
+      <c r="V194">
+        <v>1</v>
+      </c>
+      <c r="W194">
+        <v>1</v>
+      </c>
+      <c r="X194">
+        <v>1</v>
+      </c>
+      <c r="Y194">
+        <v>1</v>
+      </c>
+      <c r="Z194">
+        <v>1</v>
+      </c>
+      <c r="AA194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:27">
       <c r="A195" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>1</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="B195" s="1"/>
       <c r="C195">
         <v>1</v>
       </c>
@@ -16449,14 +16839,66 @@
       <c r="I195">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:21">
+      <c r="J195">
+        <v>1</v>
+      </c>
+      <c r="K195">
+        <v>1</v>
+      </c>
+      <c r="L195">
+        <v>1</v>
+      </c>
+      <c r="M195">
+        <v>1</v>
+      </c>
+      <c r="N195">
+        <v>1</v>
+      </c>
+      <c r="O195">
+        <v>1</v>
+      </c>
+      <c r="P195">
+        <v>1</v>
+      </c>
+      <c r="Q195">
+        <v>1</v>
+      </c>
+      <c r="R195">
+        <v>1</v>
+      </c>
+      <c r="S195">
+        <v>1</v>
+      </c>
+      <c r="T195">
+        <v>1</v>
+      </c>
+      <c r="U195">
+        <v>1</v>
+      </c>
+      <c r="V195">
+        <v>1</v>
+      </c>
+      <c r="W195">
+        <v>1</v>
+      </c>
+      <c r="X195">
+        <v>1</v>
+      </c>
+      <c r="Y195">
+        <v>1</v>
+      </c>
+      <c r="Z195">
+        <v>1</v>
+      </c>
+      <c r="AA195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:27">
       <c r="A196" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="B196" s="1"/>
       <c r="C196">
         <v>1</v>
       </c>
@@ -16478,14 +16920,66 @@
       <c r="I196">
         <v>1</v>
       </c>
-    </row>
-    <row r="197" spans="1:21">
+      <c r="J196">
+        <v>1</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="L196">
+        <v>1</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
+      </c>
+      <c r="N196">
+        <v>1</v>
+      </c>
+      <c r="O196">
+        <v>1</v>
+      </c>
+      <c r="P196">
+        <v>1</v>
+      </c>
+      <c r="Q196">
+        <v>1</v>
+      </c>
+      <c r="R196">
+        <v>1</v>
+      </c>
+      <c r="S196">
+        <v>1</v>
+      </c>
+      <c r="T196">
+        <v>1</v>
+      </c>
+      <c r="U196">
+        <v>1</v>
+      </c>
+      <c r="V196">
+        <v>1</v>
+      </c>
+      <c r="W196">
+        <v>1</v>
+      </c>
+      <c r="X196">
+        <v>1</v>
+      </c>
+      <c r="Y196">
+        <v>1</v>
+      </c>
+      <c r="Z196">
+        <v>1</v>
+      </c>
+      <c r="AA196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:27">
       <c r="A197" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>3</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="B197" s="1"/>
       <c r="C197">
         <v>1</v>
       </c>
@@ -16507,14 +17001,66 @@
       <c r="I197">
         <v>1</v>
       </c>
-    </row>
-    <row r="198" spans="1:21">
+      <c r="J197">
+        <v>1</v>
+      </c>
+      <c r="K197">
+        <v>1</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="M197">
+        <v>1</v>
+      </c>
+      <c r="N197">
+        <v>1</v>
+      </c>
+      <c r="O197">
+        <v>1</v>
+      </c>
+      <c r="P197">
+        <v>1</v>
+      </c>
+      <c r="Q197">
+        <v>1</v>
+      </c>
+      <c r="R197">
+        <v>1</v>
+      </c>
+      <c r="S197">
+        <v>1</v>
+      </c>
+      <c r="T197">
+        <v>1</v>
+      </c>
+      <c r="U197">
+        <v>1</v>
+      </c>
+      <c r="V197">
+        <v>1</v>
+      </c>
+      <c r="W197">
+        <v>1</v>
+      </c>
+      <c r="X197">
+        <v>1</v>
+      </c>
+      <c r="Y197">
+        <v>1</v>
+      </c>
+      <c r="Z197">
+        <v>1</v>
+      </c>
+      <c r="AA197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:27">
       <c r="A198" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="B198" s="1"/>
       <c r="C198">
         <v>1</v>
       </c>
@@ -16536,14 +17082,66 @@
       <c r="I198">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" spans="1:21">
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>1</v>
+      </c>
+      <c r="L198">
+        <v>1</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>1</v>
+      </c>
+      <c r="O198">
+        <v>1</v>
+      </c>
+      <c r="P198">
+        <v>1</v>
+      </c>
+      <c r="Q198">
+        <v>1</v>
+      </c>
+      <c r="R198">
+        <v>1</v>
+      </c>
+      <c r="S198">
+        <v>1</v>
+      </c>
+      <c r="T198">
+        <v>1</v>
+      </c>
+      <c r="U198">
+        <v>1</v>
+      </c>
+      <c r="V198">
+        <v>1</v>
+      </c>
+      <c r="W198">
+        <v>1</v>
+      </c>
+      <c r="X198">
+        <v>1</v>
+      </c>
+      <c r="Y198">
+        <v>1</v>
+      </c>
+      <c r="Z198">
+        <v>1</v>
+      </c>
+      <c r="AA198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:27">
       <c r="A199" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="B199" s="1"/>
       <c r="C199">
         <v>1</v>
       </c>
@@ -16565,14 +17163,66 @@
       <c r="I199">
         <v>1</v>
       </c>
-    </row>
-    <row r="200" spans="1:21">
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199">
+        <v>1</v>
+      </c>
+      <c r="L199">
+        <v>1</v>
+      </c>
+      <c r="M199">
+        <v>1</v>
+      </c>
+      <c r="N199">
+        <v>1</v>
+      </c>
+      <c r="O199">
+        <v>1</v>
+      </c>
+      <c r="P199">
+        <v>1</v>
+      </c>
+      <c r="Q199">
+        <v>1</v>
+      </c>
+      <c r="R199">
+        <v>1</v>
+      </c>
+      <c r="S199">
+        <v>1</v>
+      </c>
+      <c r="T199">
+        <v>1</v>
+      </c>
+      <c r="U199">
+        <v>1</v>
+      </c>
+      <c r="V199">
+        <v>1</v>
+      </c>
+      <c r="W199">
+        <v>1</v>
+      </c>
+      <c r="X199">
+        <v>1</v>
+      </c>
+      <c r="Y199">
+        <v>1</v>
+      </c>
+      <c r="Z199">
+        <v>1</v>
+      </c>
+      <c r="AA199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:27">
       <c r="A200" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="B200" s="1"/>
       <c r="C200">
         <v>1</v>
       </c>
@@ -16594,17 +17244,87 @@
       <c r="I200">
         <v>1</v>
       </c>
-    </row>
-    <row r="201" spans="1:21">
+      <c r="J200">
+        <v>1</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
+      </c>
+      <c r="M200">
+        <v>1</v>
+      </c>
+      <c r="N200">
+        <v>1</v>
+      </c>
+      <c r="O200">
+        <v>1</v>
+      </c>
+      <c r="P200">
+        <v>1</v>
+      </c>
+      <c r="Q200">
+        <v>1</v>
+      </c>
+      <c r="R200">
+        <v>1</v>
+      </c>
+      <c r="S200">
+        <v>1</v>
+      </c>
+      <c r="T200">
+        <v>1</v>
+      </c>
+      <c r="U200">
+        <v>1</v>
+      </c>
+      <c r="V200">
+        <v>1</v>
+      </c>
+      <c r="W200">
+        <v>1</v>
+      </c>
+      <c r="X200">
+        <v>1</v>
+      </c>
+      <c r="Y200">
+        <v>1</v>
+      </c>
+      <c r="Z200">
+        <v>1</v>
+      </c>
+      <c r="AA200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:27">
       <c r="A201" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="B201" s="1"/>
       <c r="C201">
         <v>1</v>
       </c>
+      <c r="D201">
+        <v>1</v>
+      </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
+      <c r="F201">
+        <v>1</v>
+      </c>
+      <c r="G201">
+        <v>1</v>
+      </c>
+      <c r="H201">
+        <v>1</v>
+      </c>
+      <c r="I201">
+        <v>1</v>
+      </c>
       <c r="J201">
         <v>1</v>
       </c>
@@ -16623,17 +17343,69 @@
       <c r="O201">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:21">
+      <c r="P201">
+        <v>1</v>
+      </c>
+      <c r="Q201">
+        <v>1</v>
+      </c>
+      <c r="R201">
+        <v>1</v>
+      </c>
+      <c r="S201">
+        <v>1</v>
+      </c>
+      <c r="T201">
+        <v>1</v>
+      </c>
+      <c r="U201">
+        <v>1</v>
+      </c>
+      <c r="V201">
+        <v>1</v>
+      </c>
+      <c r="W201">
+        <v>1</v>
+      </c>
+      <c r="X201">
+        <v>1</v>
+      </c>
+      <c r="Y201">
+        <v>1</v>
+      </c>
+      <c r="Z201">
+        <v>1</v>
+      </c>
+      <c r="AA201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:27">
       <c r="A202" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="B202" s="1"/>
       <c r="C202">
         <v>1</v>
       </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202">
+        <v>1</v>
+      </c>
+      <c r="F202">
+        <v>1</v>
+      </c>
+      <c r="G202">
+        <v>1</v>
+      </c>
+      <c r="H202">
+        <v>1</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
       <c r="J202">
         <v>1</v>
       </c>
@@ -16652,17 +17424,69 @@
       <c r="O202">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:21">
+      <c r="P202">
+        <v>1</v>
+      </c>
+      <c r="Q202">
+        <v>1</v>
+      </c>
+      <c r="R202">
+        <v>1</v>
+      </c>
+      <c r="S202">
+        <v>1</v>
+      </c>
+      <c r="T202">
+        <v>1</v>
+      </c>
+      <c r="U202">
+        <v>1</v>
+      </c>
+      <c r="V202">
+        <v>1</v>
+      </c>
+      <c r="W202">
+        <v>1</v>
+      </c>
+      <c r="X202">
+        <v>1</v>
+      </c>
+      <c r="Y202">
+        <v>1</v>
+      </c>
+      <c r="Z202">
+        <v>1</v>
+      </c>
+      <c r="AA202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:27">
       <c r="A203" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="B203" s="1"/>
       <c r="C203">
         <v>1</v>
       </c>
+      <c r="D203">
+        <v>1</v>
+      </c>
+      <c r="E203">
+        <v>1</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+      <c r="G203">
+        <v>1</v>
+      </c>
+      <c r="H203">
+        <v>1</v>
+      </c>
+      <c r="I203">
+        <v>1</v>
+      </c>
       <c r="J203">
         <v>1</v>
       </c>
@@ -16681,17 +17505,69 @@
       <c r="O203">
         <v>1</v>
       </c>
-    </row>
-    <row r="204" spans="1:21">
+      <c r="P203">
+        <v>1</v>
+      </c>
+      <c r="Q203">
+        <v>1</v>
+      </c>
+      <c r="R203">
+        <v>1</v>
+      </c>
+      <c r="S203">
+        <v>1</v>
+      </c>
+      <c r="T203">
+        <v>1</v>
+      </c>
+      <c r="U203">
+        <v>1</v>
+      </c>
+      <c r="V203">
+        <v>1</v>
+      </c>
+      <c r="W203">
+        <v>1</v>
+      </c>
+      <c r="X203">
+        <v>1</v>
+      </c>
+      <c r="Y203">
+        <v>1</v>
+      </c>
+      <c r="Z203">
+        <v>1</v>
+      </c>
+      <c r="AA203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:27">
       <c r="A204" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="B204" s="1"/>
       <c r="C204">
         <v>1</v>
       </c>
+      <c r="D204">
+        <v>1</v>
+      </c>
+      <c r="E204">
+        <v>1</v>
+      </c>
+      <c r="F204">
+        <v>1</v>
+      </c>
+      <c r="G204">
+        <v>1</v>
+      </c>
+      <c r="H204">
+        <v>1</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
       <c r="J204">
         <v>1</v>
       </c>
@@ -16710,17 +17586,69 @@
       <c r="O204">
         <v>1</v>
       </c>
-    </row>
-    <row r="205" spans="1:21">
+      <c r="P204">
+        <v>1</v>
+      </c>
+      <c r="Q204">
+        <v>1</v>
+      </c>
+      <c r="R204">
+        <v>1</v>
+      </c>
+      <c r="S204">
+        <v>1</v>
+      </c>
+      <c r="T204">
+        <v>1</v>
+      </c>
+      <c r="U204">
+        <v>1</v>
+      </c>
+      <c r="V204">
+        <v>1</v>
+      </c>
+      <c r="W204">
+        <v>1</v>
+      </c>
+      <c r="X204">
+        <v>1</v>
+      </c>
+      <c r="Y204">
+        <v>1</v>
+      </c>
+      <c r="Z204">
+        <v>1</v>
+      </c>
+      <c r="AA204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:27">
       <c r="A205" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="B205" s="1"/>
       <c r="C205">
         <v>1</v>
       </c>
+      <c r="D205">
+        <v>1</v>
+      </c>
+      <c r="E205">
+        <v>1</v>
+      </c>
+      <c r="F205">
+        <v>1</v>
+      </c>
+      <c r="G205">
+        <v>1</v>
+      </c>
+      <c r="H205">
+        <v>1</v>
+      </c>
+      <c r="I205">
+        <v>1</v>
+      </c>
       <c r="J205">
         <v>1</v>
       </c>
@@ -16739,17 +17667,69 @@
       <c r="O205">
         <v>1</v>
       </c>
-    </row>
-    <row r="206" spans="1:21">
+      <c r="P205">
+        <v>1</v>
+      </c>
+      <c r="Q205">
+        <v>1</v>
+      </c>
+      <c r="R205">
+        <v>1</v>
+      </c>
+      <c r="S205">
+        <v>1</v>
+      </c>
+      <c r="T205">
+        <v>1</v>
+      </c>
+      <c r="U205">
+        <v>1</v>
+      </c>
+      <c r="V205">
+        <v>1</v>
+      </c>
+      <c r="W205">
+        <v>1</v>
+      </c>
+      <c r="X205">
+        <v>1</v>
+      </c>
+      <c r="Y205">
+        <v>1</v>
+      </c>
+      <c r="Z205">
+        <v>1</v>
+      </c>
+      <c r="AA205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:27">
       <c r="A206" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="B206" s="1"/>
       <c r="C206">
         <v>1</v>
       </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206">
+        <v>1</v>
+      </c>
+      <c r="F206">
+        <v>1</v>
+      </c>
+      <c r="G206">
+        <v>1</v>
+      </c>
+      <c r="H206">
+        <v>1</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
       <c r="J206">
         <v>1</v>
       </c>
@@ -16768,17 +17748,87 @@
       <c r="O206">
         <v>1</v>
       </c>
-    </row>
-    <row r="207" spans="1:21">
+      <c r="P206">
+        <v>1</v>
+      </c>
+      <c r="Q206">
+        <v>1</v>
+      </c>
+      <c r="R206">
+        <v>1</v>
+      </c>
+      <c r="S206">
+        <v>1</v>
+      </c>
+      <c r="T206">
+        <v>1</v>
+      </c>
+      <c r="U206">
+        <v>1</v>
+      </c>
+      <c r="V206">
+        <v>1</v>
+      </c>
+      <c r="W206">
+        <v>1</v>
+      </c>
+      <c r="X206">
+        <v>1</v>
+      </c>
+      <c r="Y206">
+        <v>1</v>
+      </c>
+      <c r="Z206">
+        <v>1</v>
+      </c>
+      <c r="AA206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:27">
       <c r="A207" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>13</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="B207" s="1"/>
       <c r="C207">
         <v>1</v>
       </c>
+      <c r="D207">
+        <v>1</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+      <c r="G207">
+        <v>1</v>
+      </c>
+      <c r="H207">
+        <v>1</v>
+      </c>
+      <c r="I207">
+        <v>1</v>
+      </c>
+      <c r="J207">
+        <v>1</v>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="M207">
+        <v>1</v>
+      </c>
+      <c r="N207">
+        <v>1</v>
+      </c>
+      <c r="O207">
+        <v>1</v>
+      </c>
       <c r="P207">
         <v>1</v>
       </c>
@@ -16797,17 +17847,69 @@
       <c r="U207">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:21">
+      <c r="V207">
+        <v>1</v>
+      </c>
+      <c r="W207">
+        <v>1</v>
+      </c>
+      <c r="X207">
+        <v>1</v>
+      </c>
+      <c r="Y207">
+        <v>1</v>
+      </c>
+      <c r="Z207">
+        <v>1</v>
+      </c>
+      <c r="AA207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:27">
       <c r="A208" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="B208" s="1"/>
       <c r="C208">
         <v>1</v>
       </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+      <c r="F208">
+        <v>1</v>
+      </c>
+      <c r="G208">
+        <v>1</v>
+      </c>
+      <c r="H208">
+        <v>1</v>
+      </c>
+      <c r="I208">
+        <v>1</v>
+      </c>
+      <c r="J208">
+        <v>1</v>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+      <c r="L208">
+        <v>1</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>1</v>
+      </c>
+      <c r="O208">
+        <v>1</v>
+      </c>
       <c r="P208">
         <v>1</v>
       </c>
@@ -16824,19 +17926,71 @@
         <v>1</v>
       </c>
       <c r="U208">
+        <v>1</v>
+      </c>
+      <c r="V208">
+        <v>1</v>
+      </c>
+      <c r="W208">
+        <v>1</v>
+      </c>
+      <c r="X208">
+        <v>1</v>
+      </c>
+      <c r="Y208">
+        <v>1</v>
+      </c>
+      <c r="Z208">
+        <v>1</v>
+      </c>
+      <c r="AA208">
         <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:27">
       <c r="A209" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="B209" s="1"/>
       <c r="C209">
         <v>1</v>
       </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="E209">
+        <v>1</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209">
+        <v>1</v>
+      </c>
+      <c r="H209">
+        <v>1</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209">
+        <v>1</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>1</v>
+      </c>
+      <c r="O209">
+        <v>1</v>
+      </c>
       <c r="P209">
         <v>1</v>
       </c>
@@ -16853,19 +18007,71 @@
         <v>1</v>
       </c>
       <c r="U209">
+        <v>1</v>
+      </c>
+      <c r="V209">
+        <v>1</v>
+      </c>
+      <c r="W209">
+        <v>1</v>
+      </c>
+      <c r="X209">
+        <v>1</v>
+      </c>
+      <c r="Y209">
+        <v>1</v>
+      </c>
+      <c r="Z209">
+        <v>1</v>
+      </c>
+      <c r="AA209">
         <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:27">
       <c r="A210" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="B210" s="1"/>
       <c r="C210">
         <v>1</v>
       </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+      <c r="E210">
+        <v>1</v>
+      </c>
+      <c r="F210">
+        <v>1</v>
+      </c>
+      <c r="G210">
+        <v>1</v>
+      </c>
+      <c r="H210">
+        <v>1</v>
+      </c>
+      <c r="I210">
+        <v>1</v>
+      </c>
+      <c r="J210">
+        <v>1</v>
+      </c>
+      <c r="K210">
+        <v>1</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>1</v>
+      </c>
+      <c r="N210">
+        <v>1</v>
+      </c>
+      <c r="O210">
+        <v>1</v>
+      </c>
       <c r="P210">
         <v>1</v>
       </c>
@@ -16882,19 +18088,71 @@
         <v>1</v>
       </c>
       <c r="U210">
+        <v>1</v>
+      </c>
+      <c r="V210">
+        <v>1</v>
+      </c>
+      <c r="W210">
+        <v>1</v>
+      </c>
+      <c r="X210">
+        <v>1</v>
+      </c>
+      <c r="Y210">
+        <v>1</v>
+      </c>
+      <c r="Z210">
+        <v>1</v>
+      </c>
+      <c r="AA210">
         <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:27">
       <c r="A211" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="B211" s="1"/>
       <c r="C211">
         <v>1</v>
       </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+      <c r="E211">
+        <v>1</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211">
+        <v>1</v>
+      </c>
+      <c r="H211">
+        <v>1</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211">
+        <v>1</v>
+      </c>
+      <c r="K211">
+        <v>1</v>
+      </c>
+      <c r="L211">
+        <v>1</v>
+      </c>
+      <c r="M211">
+        <v>1</v>
+      </c>
+      <c r="N211">
+        <v>1</v>
+      </c>
+      <c r="O211">
+        <v>1</v>
+      </c>
       <c r="P211">
         <v>1</v>
       </c>
@@ -16911,19 +18169,71 @@
         <v>1</v>
       </c>
       <c r="U211">
+        <v>1</v>
+      </c>
+      <c r="V211">
+        <v>1</v>
+      </c>
+      <c r="W211">
+        <v>1</v>
+      </c>
+      <c r="X211">
+        <v>1</v>
+      </c>
+      <c r="Y211">
+        <v>1</v>
+      </c>
+      <c r="Z211">
+        <v>1</v>
+      </c>
+      <c r="AA211">
         <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:27">
       <c r="A212" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="B212" s="1"/>
       <c r="C212">
         <v>1</v>
       </c>
+      <c r="D212">
+        <v>1</v>
+      </c>
+      <c r="E212">
+        <v>1</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212">
+        <v>1</v>
+      </c>
+      <c r="H212">
+        <v>1</v>
+      </c>
+      <c r="I212">
+        <v>1</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212">
+        <v>1</v>
+      </c>
+      <c r="M212">
+        <v>1</v>
+      </c>
+      <c r="N212">
+        <v>1</v>
+      </c>
+      <c r="O212">
+        <v>1</v>
+      </c>
       <c r="P212">
         <v>1</v>
       </c>
@@ -16940,128 +18250,95 @@
         <v>1</v>
       </c>
       <c r="U212">
+        <v>1</v>
+      </c>
+      <c r="V212">
+        <v>1</v>
+      </c>
+      <c r="W212">
+        <v>1</v>
+      </c>
+      <c r="X212">
+        <v>1</v>
+      </c>
+      <c r="Y212">
+        <v>1</v>
+      </c>
+      <c r="Z212">
+        <v>1</v>
+      </c>
+      <c r="AA212">
         <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:27">
       <c r="A213" s="1" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C213">
         <v>1</v>
       </c>
-      <c r="V213">
-        <v>1</v>
-      </c>
-      <c r="W213">
-        <v>1</v>
-      </c>
-      <c r="X213">
-        <v>1</v>
-      </c>
-      <c r="Y213">
-        <v>1</v>
-      </c>
-      <c r="Z213">
-        <v>1</v>
-      </c>
-      <c r="AA213">
+      <c r="D213">
         <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:27">
       <c r="A214" s="1" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C214">
         <v>1</v>
       </c>
-      <c r="V214">
-        <v>1</v>
-      </c>
-      <c r="W214">
-        <v>1</v>
-      </c>
-      <c r="X214">
-        <v>1</v>
-      </c>
-      <c r="Y214">
-        <v>1</v>
-      </c>
-      <c r="Z214">
-        <v>1</v>
-      </c>
-      <c r="AA214">
+      <c r="D214">
+        <v>1</v>
+      </c>
+      <c r="G214">
         <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:27">
       <c r="A215" s="1" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
-      <c r="V215">
-        <v>1</v>
-      </c>
-      <c r="W215">
-        <v>1</v>
-      </c>
-      <c r="X215">
-        <v>1</v>
-      </c>
-      <c r="Y215">
-        <v>1</v>
-      </c>
-      <c r="Z215">
-        <v>1</v>
-      </c>
-      <c r="AA215">
+      <c r="J215">
+        <v>1</v>
+      </c>
+      <c r="M215">
         <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:27">
       <c r="A216" s="1" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C216">
         <v>1</v>
       </c>
-      <c r="V216">
-        <v>1</v>
-      </c>
-      <c r="W216">
-        <v>1</v>
-      </c>
-      <c r="X216">
-        <v>1</v>
-      </c>
-      <c r="Y216">
-        <v>1</v>
-      </c>
-      <c r="Z216">
-        <v>1</v>
-      </c>
-      <c r="AA216">
+      <c r="J216">
+        <v>1</v>
+      </c>
+      <c r="M216">
         <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:27">
       <c r="A217" s="1" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>23</v>
@@ -17069,85 +18346,103 @@
       <c r="C217">
         <v>1</v>
       </c>
-      <c r="V217">
-        <v>1</v>
-      </c>
-      <c r="W217">
-        <v>1</v>
-      </c>
-      <c r="X217">
-        <v>1</v>
-      </c>
-      <c r="Y217">
-        <v>1</v>
-      </c>
-      <c r="Z217">
-        <v>1</v>
-      </c>
-      <c r="AA217">
+      <c r="J217">
+        <v>1</v>
+      </c>
+      <c r="M217">
         <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:27">
       <c r="A218" s="1" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C218">
         <v>1</v>
       </c>
-      <c r="V218">
-        <v>1</v>
-      </c>
-      <c r="W218">
-        <v>1</v>
-      </c>
-      <c r="X218">
-        <v>1</v>
-      </c>
-      <c r="Y218">
-        <v>1</v>
-      </c>
-      <c r="Z218">
-        <v>1</v>
-      </c>
-      <c r="AA218">
+      <c r="D218">
+        <v>1</v>
+      </c>
+      <c r="E218">
+        <v>1</v>
+      </c>
+      <c r="F218">
+        <v>1</v>
+      </c>
+      <c r="G218">
+        <v>1</v>
+      </c>
+      <c r="H218">
+        <v>1</v>
+      </c>
+      <c r="I218">
         <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:27">
       <c r="A219" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C219">
         <v>1</v>
       </c>
+      <c r="D219">
+        <v>1</v>
+      </c>
       <c r="E219">
+        <v>1</v>
+      </c>
+      <c r="F219">
+        <v>1</v>
+      </c>
+      <c r="G219">
+        <v>1</v>
+      </c>
+      <c r="H219">
+        <v>1</v>
+      </c>
+      <c r="I219">
         <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:27">
       <c r="A220" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
+      <c r="D220">
+        <v>1</v>
+      </c>
+      <c r="E220">
+        <v>1</v>
+      </c>
       <c r="F220">
+        <v>1</v>
+      </c>
+      <c r="G220">
+        <v>1</v>
+      </c>
+      <c r="H220">
+        <v>1</v>
+      </c>
+      <c r="I220">
         <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:27">
       <c r="A221" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>4</v>
@@ -17155,13 +18450,28 @@
       <c r="C221">
         <v>1</v>
       </c>
+      <c r="D221">
+        <v>1</v>
+      </c>
+      <c r="E221">
+        <v>1</v>
+      </c>
+      <c r="F221">
+        <v>1</v>
+      </c>
+      <c r="G221">
+        <v>1</v>
+      </c>
       <c r="H221">
+        <v>1</v>
+      </c>
+      <c r="I221">
         <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:27">
       <c r="A222" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>5</v>
@@ -17169,60 +18479,135 @@
       <c r="C222">
         <v>1</v>
       </c>
+      <c r="D222">
+        <v>1</v>
+      </c>
+      <c r="E222">
+        <v>1</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222">
+        <v>1</v>
+      </c>
+      <c r="H222">
+        <v>1</v>
+      </c>
       <c r="I222">
         <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:27">
       <c r="A223" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
-      <c r="K223">
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223">
+        <v>1</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+      <c r="G223">
+        <v>1</v>
+      </c>
+      <c r="H223">
+        <v>1</v>
+      </c>
+      <c r="I223">
         <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:27">
       <c r="A224" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
+      <c r="J224">
+        <v>1</v>
+      </c>
+      <c r="K224">
+        <v>1</v>
+      </c>
       <c r="L224">
+        <v>1</v>
+      </c>
+      <c r="M224">
+        <v>1</v>
+      </c>
+      <c r="N224">
+        <v>1</v>
+      </c>
+      <c r="O224">
         <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:27">
       <c r="A225" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
+      <c r="J225">
+        <v>1</v>
+      </c>
+      <c r="K225">
+        <v>1</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>1</v>
+      </c>
       <c r="N225">
+        <v>1</v>
+      </c>
+      <c r="O225">
         <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:27">
       <c r="A226" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C226">
+        <v>1</v>
+      </c>
+      <c r="J226">
+        <v>1</v>
+      </c>
+      <c r="K226">
+        <v>1</v>
+      </c>
+      <c r="L226">
+        <v>1</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
         <v>1</v>
       </c>
       <c r="O226">
@@ -17231,54 +18616,114 @@
     </row>
     <row r="227" spans="1:27">
       <c r="A227" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
-      <c r="Q227">
+      <c r="J227">
+        <v>1</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+      <c r="L227">
+        <v>1</v>
+      </c>
+      <c r="M227">
+        <v>1</v>
+      </c>
+      <c r="N227">
+        <v>1</v>
+      </c>
+      <c r="O227">
         <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:27">
       <c r="A228" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
-      <c r="R228">
+      <c r="J228">
+        <v>1</v>
+      </c>
+      <c r="K228">
+        <v>1</v>
+      </c>
+      <c r="L228">
+        <v>1</v>
+      </c>
+      <c r="M228">
+        <v>1</v>
+      </c>
+      <c r="N228">
+        <v>1</v>
+      </c>
+      <c r="O228">
         <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:27">
       <c r="A229" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C229">
         <v>1</v>
       </c>
-      <c r="T229">
+      <c r="J229">
+        <v>1</v>
+      </c>
+      <c r="K229">
+        <v>1</v>
+      </c>
+      <c r="L229">
+        <v>1</v>
+      </c>
+      <c r="M229">
+        <v>1</v>
+      </c>
+      <c r="N229">
+        <v>1</v>
+      </c>
+      <c r="O229">
         <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:27">
       <c r="A230" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C230">
+        <v>1</v>
+      </c>
+      <c r="P230">
+        <v>1</v>
+      </c>
+      <c r="Q230">
+        <v>1</v>
+      </c>
+      <c r="R230">
+        <v>1</v>
+      </c>
+      <c r="S230">
+        <v>1</v>
+      </c>
+      <c r="T230">
         <v>1</v>
       </c>
       <c r="U230">
@@ -17287,57 +18732,544 @@
     </row>
     <row r="231" spans="1:27">
       <c r="A231" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
-      <c r="W231">
+      <c r="P231">
+        <v>1</v>
+      </c>
+      <c r="Q231">
+        <v>1</v>
+      </c>
+      <c r="R231">
+        <v>1</v>
+      </c>
+      <c r="S231">
+        <v>1</v>
+      </c>
+      <c r="T231">
+        <v>1</v>
+      </c>
+      <c r="U231">
         <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:27">
       <c r="A232" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C232">
         <v>1</v>
       </c>
-      <c r="X232">
+      <c r="P232">
+        <v>1</v>
+      </c>
+      <c r="Q232">
+        <v>1</v>
+      </c>
+      <c r="R232">
+        <v>1</v>
+      </c>
+      <c r="S232">
+        <v>1</v>
+      </c>
+      <c r="T232">
+        <v>1</v>
+      </c>
+      <c r="U232">
         <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:27">
       <c r="A233" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
-      <c r="Z233">
+      <c r="P233">
+        <v>1</v>
+      </c>
+      <c r="Q233">
+        <v>1</v>
+      </c>
+      <c r="R233">
+        <v>1</v>
+      </c>
+      <c r="S233">
+        <v>1</v>
+      </c>
+      <c r="T233">
+        <v>1</v>
+      </c>
+      <c r="U233">
         <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:27">
       <c r="A234" s="1" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B234" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+      <c r="P234">
+        <v>1</v>
+      </c>
+      <c r="Q234">
+        <v>1</v>
+      </c>
+      <c r="R234">
+        <v>1</v>
+      </c>
+      <c r="S234">
+        <v>1</v>
+      </c>
+      <c r="T234">
+        <v>1</v>
+      </c>
+      <c r="U234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:27">
+      <c r="A235" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C235">
+        <v>1</v>
+      </c>
+      <c r="P235">
+        <v>1</v>
+      </c>
+      <c r="Q235">
+        <v>1</v>
+      </c>
+      <c r="R235">
+        <v>1</v>
+      </c>
+      <c r="S235">
+        <v>1</v>
+      </c>
+      <c r="T235">
+        <v>1</v>
+      </c>
+      <c r="U235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:27">
+      <c r="A236" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+      <c r="V236">
+        <v>1</v>
+      </c>
+      <c r="W236">
+        <v>1</v>
+      </c>
+      <c r="X236">
+        <v>1</v>
+      </c>
+      <c r="Y236">
+        <v>1</v>
+      </c>
+      <c r="Z236">
+        <v>1</v>
+      </c>
+      <c r="AA236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:27">
+      <c r="A237" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C237">
+        <v>1</v>
+      </c>
+      <c r="V237">
+        <v>1</v>
+      </c>
+      <c r="W237">
+        <v>1</v>
+      </c>
+      <c r="X237">
+        <v>1</v>
+      </c>
+      <c r="Y237">
+        <v>1</v>
+      </c>
+      <c r="Z237">
+        <v>1</v>
+      </c>
+      <c r="AA237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:27">
+      <c r="A238" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C238">
+        <v>1</v>
+      </c>
+      <c r="V238">
+        <v>1</v>
+      </c>
+      <c r="W238">
+        <v>1</v>
+      </c>
+      <c r="X238">
+        <v>1</v>
+      </c>
+      <c r="Y238">
+        <v>1</v>
+      </c>
+      <c r="Z238">
+        <v>1</v>
+      </c>
+      <c r="AA238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:27">
+      <c r="A239" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C239">
+        <v>1</v>
+      </c>
+      <c r="V239">
+        <v>1</v>
+      </c>
+      <c r="W239">
+        <v>1</v>
+      </c>
+      <c r="X239">
+        <v>1</v>
+      </c>
+      <c r="Y239">
+        <v>1</v>
+      </c>
+      <c r="Z239">
+        <v>1</v>
+      </c>
+      <c r="AA239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:27">
+      <c r="A240" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C234">
-        <v>1</v>
-      </c>
-      <c r="AA234">
+      <c r="C240">
+        <v>1</v>
+      </c>
+      <c r="V240">
+        <v>1</v>
+      </c>
+      <c r="W240">
+        <v>1</v>
+      </c>
+      <c r="X240">
+        <v>1</v>
+      </c>
+      <c r="Y240">
+        <v>1</v>
+      </c>
+      <c r="Z240">
+        <v>1</v>
+      </c>
+      <c r="AA240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:27">
+      <c r="A241" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C241">
+        <v>1</v>
+      </c>
+      <c r="V241">
+        <v>1</v>
+      </c>
+      <c r="W241">
+        <v>1</v>
+      </c>
+      <c r="X241">
+        <v>1</v>
+      </c>
+      <c r="Y241">
+        <v>1</v>
+      </c>
+      <c r="Z241">
+        <v>1</v>
+      </c>
+      <c r="AA241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:27">
+      <c r="A242" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:27">
+      <c r="A243" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C243">
+        <v>1</v>
+      </c>
+      <c r="F243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:27">
+      <c r="A244" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C244">
+        <v>1</v>
+      </c>
+      <c r="H244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:27">
+      <c r="A245" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C245">
+        <v>1</v>
+      </c>
+      <c r="I245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:27">
+      <c r="A246" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C246">
+        <v>1</v>
+      </c>
+      <c r="K246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:27">
+      <c r="A247" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+      <c r="L247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:27">
+      <c r="A248" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C248">
+        <v>1</v>
+      </c>
+      <c r="N248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:27">
+      <c r="A249" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C249">
+        <v>1</v>
+      </c>
+      <c r="O249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:27">
+      <c r="A250" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C250">
+        <v>1</v>
+      </c>
+      <c r="Q250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:27">
+      <c r="A251" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C251">
+        <v>1</v>
+      </c>
+      <c r="R251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:27">
+      <c r="A252" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C252">
+        <v>1</v>
+      </c>
+      <c r="T252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:27">
+      <c r="A253" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C253">
+        <v>1</v>
+      </c>
+      <c r="U253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:27">
+      <c r="A254" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C254">
+        <v>1</v>
+      </c>
+      <c r="W254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:27">
+      <c r="A255" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C255">
+        <v>1</v>
+      </c>
+      <c r="X255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:27">
+      <c r="A256" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C256">
+        <v>1</v>
+      </c>
+      <c r="Z256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:27">
+      <c r="A257" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C257">
+        <v>1</v>
+      </c>
+      <c r="AA257">
         <v>1</v>
       </c>
     </row>
